--- a/rediseno_2026/Documento unificado/Revisión del documento unificado - calificación HCU 32-2025, términos y correcciones.xlsx
+++ b/rediseno_2026/Documento unificado/Revisión del documento unificado - calificación HCU 32-2025, términos y correcciones.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requisitos'!$A$3:$I$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Puntos'!$A$3:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Términos'!$A$3:$I$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correcciones'!$A$3:$G$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correcciones'!$A$3:$G$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Coherencia'!$A$3:$H$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Calificación frente a la Resolución HCU N.º 032/2025, términos que se cambian a mano, correcciones aplicadas y coherencia pendiente.</t>
+          <t>Calificación frente a la Resolución HCU N.º 032/2025, términos de coherencia, correcciones aplicadas (incluye datos de matrícula 2026) y coherencia pendiente.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano</t>
+          <t>Términos de coherencia (aplicados)</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano</t>
+          <t>Términos de coherencia (aplicados)</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano</t>
+          <t>Términos de coherencia (aplicados)</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano</t>
+          <t>Términos de coherencia (aplicados)</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano</t>
+          <t>Términos de coherencia (aplicados)</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Términos que se cambian a mano, por punto y página</t>
+          <t>Términos de coherencia, por punto y página</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Página según el Word revisado. «Mantener» y «Revisar» indican menciones que probablemente no deben cambiarse. Los índices se actualizan solos al abrir el Word.</t>
+          <t>Ya aplicados en el Word revisado (Seguimiento = Corregido). «Mantener» indica menciones que no se cambian. Página según el Word antes del cambio.</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5671,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I9" s="10" t="n"/>
@@ -5712,12 +5712,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I10" s="10" t="n"/>
@@ -5758,10 +5758,14 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -5794,12 +5798,12 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I12" s="10" t="n"/>
@@ -5835,12 +5839,12 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I13" s="10" t="n"/>
@@ -5876,12 +5880,12 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I14" s="10" t="n"/>
@@ -5917,12 +5921,12 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I15" s="10" t="n"/>
@@ -5963,10 +5967,14 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -6004,10 +6012,14 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -6045,10 +6057,14 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -6086,10 +6102,14 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6127,10 +6147,14 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -6168,10 +6192,14 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6209,10 +6237,14 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6455,10 +6487,14 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -6496,10 +6532,14 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6537,10 +6577,14 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -6619,10 +6663,14 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -6655,12 +6703,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual (o «del Área Contextual»)</t>
+          <t>Mantener: ya dice «Área Contextual»</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I33" s="10" t="n"/>
@@ -6701,10 +6749,14 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6865,10 +6917,14 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -6906,10 +6962,14 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7398,10 +7458,14 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -7439,10 +7503,14 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7480,10 +7548,14 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -7521,10 +7593,14 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -7603,10 +7679,14 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -7644,10 +7724,14 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -7685,10 +7769,14 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -7726,10 +7814,14 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -7767,10 +7859,14 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -7808,10 +7904,14 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -7844,12 +7944,12 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Revisar: es el nombre de la Resolución N.º 07/2024; mantener si es su denominación literal</t>
+          <t>Mantener: es el nombre de la Resolución N.º 07/2024 (decisión de la comisión)</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="I62" s="10" t="n"/>
@@ -7890,10 +7990,14 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -7972,10 +8076,14 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -8013,10 +8121,14 @@
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8136,10 +8248,14 @@
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -8382,10 +8498,14 @@
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -8418,15 +8538,19 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Revisar: podría quedar «para el Rediseño Curricular de la Licenciatura en Contaduría Pública»</t>
+          <t>Rediseño Curricular de la Licenciatura en Contaduría Pública (frase completa: «para el Rediseño Curricular de la Licenciatura en Contaduría Pública»)</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -8464,10 +8588,14 @@
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -8587,10 +8715,14 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8628,10 +8760,14 @@
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -8669,10 +8805,14 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -8710,10 +8850,14 @@
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -8751,10 +8895,14 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -8792,10 +8940,14 @@
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -8833,10 +8985,14 @@
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -8874,10 +9030,14 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -8915,10 +9075,14 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -8956,10 +9120,14 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -8997,10 +9165,14 @@
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I90" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -9038,10 +9210,14 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I91" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -9079,10 +9255,14 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -9120,10 +9300,14 @@
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I93" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -9161,10 +9345,14 @@
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I94" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -9202,10 +9390,14 @@
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I95" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -9243,10 +9435,14 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I96" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9284,10 +9480,14 @@
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I97" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -9325,10 +9525,14 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I98" s="10" t="n"/>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Aplicado en el Word revisado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:I98"/>
@@ -9362,7 +9566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10298,29 +10502,25 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Contaduría publica</t>
+          <t>Estudiantes matriculados, gestión 2025</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Pública</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El Plan Estratégico Institucional de la Carrera de Contaduría publica forma parte del plan estratégico Institucional de </t>
-        </is>
-      </c>
+          <t>Estudiantes matriculados, gestión 2026</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10331,29 +10531,25 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>kardixtas</t>
+          <t>4.283</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>kardexistas</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Apoyo académico y administrativo: Encargado de Kárdex, con una encargada de Kárdex I y dos kardixtas académicos; dos enc</t>
-        </is>
-      </c>
+          <t>4.296: 3.743 antiguos y 553 nuevos, en la sede de La Paz</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10364,29 +10560,25 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Estudiantes inscritos, gestión 2025</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>Estudiantes inscritos, gestión 2026</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10397,29 +10589,25 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>3.247: 3.143 en la sede de La Paz y 104 en las sedes desconcentradas</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Total Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>3.116 en la sede de La Paz; las sedes desconcentradas registraron 104 inscritos en 2025</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
       <c r="F37" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10430,7 +10618,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -10440,17 +10628,17 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>Contaduría publica</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>Contaduría Pública</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>El área contable y de auditoria concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de</t>
+          <t xml:space="preserve">El Plan Estratégico Institucional de la Carrera de Contaduría publica forma parte del plan estratégico Institucional de </t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -10463,7 +10651,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -10473,17 +10661,17 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>kardixtas</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>kardexistas</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Área Contable y de Auditoria</t>
+          <t>Apoyo académico y administrativo: Encargado de Kárdex, con una encargada de Kárdex I y dos kardixtas académicos; dos enc</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -10496,29 +10684,25 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Con una población de 4.283 estudiantes matriculados y 3.143 inscritos en la gestión 2025, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Total Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>Con una población de 4.296 estudiantes matriculados y 3.116 inscritos en la gestión 2026, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10615,7 +10799,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de</t>
+          <t>El área contable y de auditoria concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -10628,27 +10812,27 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y articulación con los diplomados y </t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -10661,7 +10845,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -10671,17 +10855,17 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>curgricular</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>curricular</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>El rediseño es el instrumento curgricular para cumplir el OE 1.3 y respalda las metas de acreditación de la Carrera</t>
+          <t>Total Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -10694,7 +10878,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -10704,17 +10888,17 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Aplicaciones para auditoria y finanzas</t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -10727,7 +10911,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>4.1.4</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -10737,17 +10921,17 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Adminisión</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Admisión</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>IES 1 Requisitos de Ingreso al Programa: Garantiza la equidad, transparencia y meritocracia en los procesos de selección</t>
+          <t>Total Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -10760,27 +10944,27 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
+          <t>auditoría</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>los grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y la articulación de la graduaci</t>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -10793,29 +10977,25 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>4.3.4</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Sector Publico</t>
+          <t>El área contable y de auditoría concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Sector Público</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Incorporar los contenidos emergentes de mayor demanda: Normas del Sector Publico, NIIF y NIIF de Sostenibilidad, asegura</t>
-        </is>
-      </c>
+          <t>El área contable y de auditoría concentran 73 cargas horarias y el Área Contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10826,29 +11006,25 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>CPA-302 Contabilidad de Costos y Gestión, CPA-305 Sistemas Contables ERP y Análisis de Datos, CPA-406 Ética e Independen</t>
-        </is>
-      </c>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10859,29 +11035,21 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
+          <t>Datos de matrícula, gestión 2026</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr"/>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>CPA-501 Auditoría Operativa, CPA-502 Gabinete de Auditoría Financiera, CPA-504 Auditoría Gubernamental, CPA-508 Auditorí</t>
-        </is>
-      </c>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10892,29 +11060,25 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.283 en 2025, lo que representa una reducción del 8,97 %.</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.296 en 2026, lo que representa una reducción del 8,69 %.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10925,29 +11089,25 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.143, equivalente a una disminución del 0,29 %.</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.116, equivalente a una disminución del 1,14 %.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10958,29 +11118,25 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.140 en 2025, que representan el 26,62 % del total de matriculados.</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.180 en 2026, aunque aumentó respecto de los 1.140 de 2025, y representa el 27,47 % del total de matriculados.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10991,29 +11147,25 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
-        </is>
-      </c>
+          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11024,29 +11176,25 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son troncales, el 67,</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
-        </is>
-      </c>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11057,29 +11205,25 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Subtotal troncal</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
-        </is>
-      </c>
+          <t>Subtotal Área Contable y de Auditoría</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11090,29 +11234,25 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr"/>
       <c r="F58" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11123,22 +11263,22 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Formato</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Texto en color rojo (Cuadro 4 de mesas, Cuadro 5 de grados, examen por ciclos y listas de ciclos)</t>
+          <t>Subtotal contextual</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Color automático</t>
+          <t>Subtotal Área Contextual</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr"/>
@@ -11152,18 +11292,22 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Estructura y formato</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr"/>
+          <t>Término: Área Contextual</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>La estructura muestra un rasgo que condiciona el rediseño: las áreas contextuales se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación es secuencial</t>
+        </is>
+      </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Se eliminó el comentario de la Lic. Carlos Gonzales Alanes y el color rojo del punto 5, tras revisar los nombres de las asignaturas.</t>
+          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
@@ -11177,29 +11321,25 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior</t>
-        </is>
-      </c>
+          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11210,29 +11350,21 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
-        </is>
-      </c>
+          <t>Datos de matrícula, gestión 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr"/>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
-        </is>
-      </c>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180 | 72,53</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11243,22 +11375,22 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Descripción del grado intermedio TUM</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Aprobación de todas las asignaturas del Primer y Segundo año, 16 asignaturas, en el tiempo determinado (dos años continuos bajo modalidad anual)</t>
+          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2025</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumplimiento de la Resolución HCU Nº 426/2024</t>
+          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2026</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
@@ -11272,29 +11404,25 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Presupuestos y Contabilidad Gubernamental</t>
+          <t>Matriculados e inscritos, 2025</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Presupuestos y Contabilidad Gubernamental</t>
-        </is>
-      </c>
+          <t>Matriculados e inscritos, 2026</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11305,29 +11433,25 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>4.283 y 3.143</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
-        </is>
-      </c>
+          <t>4.296 y 3.116</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11338,29 +11462,25 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos: Público y Privado</t>
+          <t>La matrícula cayó 8,97 % desde 2021</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría de Proyectos: Público y Privado</t>
-        </is>
-      </c>
+          <t>La matrícula cayó 8,69 % desde 2021</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr"/>
       <c r="F66" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11371,29 +11491,25 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras</t>
+          <t>33,01 % en 2021 y 26,62 % en 2025</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras y Servicios Relacionados</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría de Entidades Financieras</t>
-        </is>
-      </c>
+          <t>33,01 % en 2021 y 27,47 % en 2026</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11404,27 +11520,27 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>), el estudiante que concluya las 43 asignaturas del presente plan, podrá optar por una de las siguientes seis modalidades</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>) y con el Reglamento de Modalidades de Graduación de la Carrera incorporado en el punto 13.1.4, el estudiante que concluya las 43 asignaturas del presente plan podrá optar por una de las siguientes siete modalidades</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>En estricta concordancia con el Reglamento General de Tipos y Modalidades de Graduación del SUB (aprobado en los congres</t>
+          <t xml:space="preserve">Grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y articulación con los diplomados y </t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -11437,27 +11553,27 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>dedicación exclusiva durante un periodo máximo de 8 meses.</t>
+          <t>curgricular</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>dedicación exclusiva durante un periodo máximo de ocho (8) meses, con un mínimo de 1.280 horas de trabajo efectivo, conforme a los Artículos 46 y 47 del Reglamento de Modalidades de Graduación.</t>
+          <t>curricular</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Requisitos Específicos: El estudiante debe tener un promedio académico acumulado no menor a sesenta (60) puntos y dedica</t>
+          <t>El rediseño es el instrumento curgricular para cumplir el OE 1.3 y respalda las metas de acreditación de la Carrera</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -11470,25 +11586,29 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Buena</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Bueno</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr"/>
+          <t>auditoría</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Aplicaciones para auditoria y finanzas</t>
+        </is>
+      </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11499,22 +11619,22 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Sobresaliente – Con recomendación de publicación</t>
+          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público Autorizado debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y socio</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Sobresaliente</t>
+          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y sociológicas.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr"/>
@@ -11528,22 +11648,22 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Excelente – Con mención honorífica y recomendación de publicación</t>
+          <t>Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público Autorizado aplica</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Excelente – Excelencia</t>
+          <t xml:space="preserve">Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público aplica su juicio </t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
@@ -11557,27 +11677,27 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>como mínimo tres (3) veces al año</t>
+          <t>Adminisión</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>como mínimo cuatro (4) veces al año, cada convocatoria en tres (3) semanas continuas, una por ciclo</t>
+          <t>Admisión</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
+          <t>IES 1 Requisitos de Ingreso al Programa: Garantiza la equidad, transparencia y meritocracia en los procesos de selección</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -11590,29 +11710,25 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.2.6</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>24 horas de anticipación al examen.</t>
+          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público Autorizado</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>24 horas de anticipación al examen. El postulante debe aprobar los tres ciclos en un plazo máximo de doce (12) meses calendario desde su inscripción al primer ciclo, y quien repruebe tres (3) veces un mismo ciclo queda inhabilitado para esta modalidad, conforme a los Artículos 60 a 67 del Reglamento de Modalidades de Graduación.</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
-        </is>
-      </c>
+          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr"/>
       <c r="F74" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11623,27 +11739,27 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Ciclo Servicios</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Ciclo de Servicios</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Ciclo Servicios de Aseguramiento</t>
+          <t>los grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y la articulación de la graduaci</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
@@ -11656,25 +11772,29 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.3.4</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Haber aprobado el 100% de las 43 asignaturas en primera instancia (sin haber recurrido a exámenes de mesa ni haber reprobado ninguna materia).</t>
+          <t>Sector Publico</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Haber aprobado el 100% de las 43 asignaturas en evaluaciones ordinarias de primera instancia, sin haber reprobado, abandonado ni cursado asignaturas en segundo turno, exámenes extraordinarios de mesa o cursos de verano destinados a subsanar reprobaciones.</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr"/>
+          <t>Sector Público</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Incorporar los contenidos emergentes de mayor demanda: Normas del Sector Publico, NIIF y NIIF de Sostenibilidad, asegura</t>
+        </is>
+      </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11685,25 +11805,29 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Haber concluido el plan de estudios dentro del tiempo reglamentario de la carrera (5 años continuos).</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Haber concluido el plan de estudios en el tiempo reglamentario de cinco (5) gestiones académicas anuales continuas, sin suspensiones voluntarias, abandonos temporales ni postergaciones de matrícula.</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr"/>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>CPA-302 Contabilidad de Costos y Gestión, CPA-305 Sistemas Contables ERP y Análisis de Datos, CPA-406 Ética e Independen</t>
+        </is>
+      </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11714,25 +11838,29 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Acreditar un promedio general ponderado cuantitativo sobresaliente (igual o superior al límite fijado por la normativa de la Facultad y la UMSA).</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Acreditar un Promedio Ponderado Acumulado (PPA) igual o superior a setenta y cinco (75) puntos a lo largo de los cinco años de estudio, conforme al Artículo 72 del Reglamento de Modalidades de Graduación.</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr"/>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>CPA-501 Auditoría Operativa, CPA-502 Gabinete de Auditoría Financiera, CPA-504 Auditoría Gubernamental, CPA-508 Auditorí</t>
+        </is>
+      </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11743,21 +11871,29 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72, requisito agregado)</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr"/>
+          <t>Ortografía</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>No registrar antecedentes disciplinarios, sanciones administrativas, procesos en Tribunal de Honor ni fallos de ética universitaria o de plagio académico.</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr"/>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Área Contable y de Auditoria</t>
+        </is>
+      </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11768,27 +11904,27 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 78)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>el estudiante de Quinto Año o egresado puede cursar</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>el estudiante que concluyó y aprobó las 43 asignaturas del plan de estudios puede cursar</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
@@ -11801,29 +11937,25 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa).</t>
+          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa). Los programas duran entre cuatro (4) y seis (6) meses y exigen un 80 % de asistencia y una nota mínima de setenta y uno (71) puntos por módulo y en el trabajo final, conforme a los Artículos 77 a 82 del Reglamento de Modalidades de Graduación.</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
-        </is>
-      </c>
+          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11834,22 +11966,22 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Comentario eliminado</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Comentario de Carlos Gonzales Alanes: "Revisar los nombres de las asignaturas por favor"</t>
+          <t>Área contextual:</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Eliminado tras ajustar los nombres a la malla</t>
+          <t>Área Contextual:</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr"/>
@@ -11863,7 +11995,7 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -11873,17 +12005,17 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
@@ -11896,27 +12028,27 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
@@ -11929,27 +12061,27 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>b. Técnico Universitario Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -11962,25 +12094,29 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Descripción del grado intermedio TUM</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">a. Técnico Universitario Medio. Conforme al Artículo Segundo de la Resolución HCU N.º 426/2024, el requisito ineludible para extender el Diploma Académico y el Título Profesional de Técnico Universitario Medio es la aprobación de todas las asignaturas de primero y segundo año en el tiempo determinado de dos años, inexcusablemente. </t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>a. Técnico Universitario Medio. Salida intermedia que conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr"/>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
+        </is>
+      </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11991,27 +12127,27 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>se aprueba con nota mínima de 51 puntos sobre 100.</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>se aprueba con nota mínima de 51 puntos sobre 100. La prueba es escrita, de resolución de casos sobre información financiera, con una duración de noventa (90) minutos, conforme a los Artículos 87 a 90 del Reglamento de Modalidades de Graduación.</t>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>b. Técnico Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de grado técnico</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
@@ -12024,29 +12160,25 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Formato</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">digital,  </t>
+          <t>Texto en color rojo (Cuadro 4 de mesas, Cuadro 5 de grados, examen por ciclos y listas de ciclos)</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>digital,</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Promover nuevos campos de investigación científica, especialmente aquellos que contribuyan a la construcción teórica de </t>
-        </is>
-      </c>
+          <t>Color automático</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12057,22 +12189,18 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Contenido duplicado eliminado</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>7.2Políticas y líneas de extensión universitaria | 7.2.1Políticas | Educación continua. La Carrera ofrece programas para diversos públicos interesados en las ares contables y financieras que son temas transversales para la gestión. | Articulación con el postgrado. La oferta de extensión se articula con la Unidad de Postgrado y con la modalidad de graduación mediante diplomado del punto 5.4.2. | Di</t>
-        </is>
-      </c>
+          <t>Estructura y formato</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr"/>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Se conserva la segunda versión de 7.2 y 7.2.1, que contiene y amplía todos los ítems de la primera</t>
+          <t>Se eliminó el comentario de la Lic. Carlos Gonzales Alanes y el color rojo del punto 5, tras revisar los nombres de las asignaturas.</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr"/>
@@ -12086,27 +12214,27 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
@@ -12119,27 +12247,27 @@
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Técnico Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
@@ -12152,29 +12280,25 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Descripción del grado intermedio TUM</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Aprobación de todas las asignaturas del Primer y Segundo año, 16 asignaturas, en el tiempo determinado (dos años continuos bajo modalidad anual)</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
-        </is>
-      </c>
+          <t>Aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumplimiento de la Resolución HCU Nº 426/2024</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr"/>
       <c r="F92" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12185,7 +12309,7 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -12195,17 +12319,17 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Público y Privado</t>
+          <t>Presupuestos y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Público y Privado</t>
+          <t>Presupuestos y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
@@ -12218,7 +12342,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -12228,17 +12352,17 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
@@ -12251,25 +12375,29 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5. Estudiantes inscritos por asignatura y paralelo</t>
+          <t>Auditoría de Proyectos: Público y Privado</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Estudiantes inscritos por asignatura y paralelo</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr"/>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Proyectos: Público y Privado</t>
+        </is>
+      </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12280,7 +12408,7 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -12290,17 +12418,17 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Auditoría de Entidades Financieras</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
+          <t>Auditoría de Entidades Financieras y Servicios Relacionados</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Auditoría de Entidades Financieras</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
@@ -12313,27 +12441,27 @@
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>), el estudiante que concluya las 43 asignaturas del presente plan, podrá optar por una de las siguientes seis modalidades</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>) y con el Reglamento de Modalidades de Graduación de la Carrera incorporado en el punto 13.1.4, el estudiante que concluya las 43 asignaturas del presente plan podrá optar por una de las siguientes siete modalidades</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>En estricta concordancia con el Reglamento General de Tipos y Modalidades de Graduación del SUB (aprobado en los congres</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
@@ -12346,27 +12474,27 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>dedicación exclusiva durante un periodo máximo de 8 meses.</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>dedicación exclusiva durante un periodo máximo de ocho (8) meses, con un mínimo de 1.280 horas de trabajo efectivo, conforme a los Artículos 46 y 47 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Requisitos Específicos: El estudiante debe tener un promedio académico acumulado no menor a sesenta (60) puntos y dedica</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
@@ -12379,29 +12507,25 @@
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Aprobado – Buena</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
-        </is>
-      </c>
+          <t>Aprobado – Bueno</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
       <c r="F99" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12412,29 +12536,25 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Sobresaliente – Con recomendación de publicación</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
+          <t>Aprobado – Sobresaliente</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12445,29 +12565,25 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Publica</t>
+          <t>Excelente – Con mención honorífica y recomendación de publicación</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Pública</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>La Carrera de Contaduría Publica actualmente cuenta con la siguiente bibliografía:</t>
-        </is>
-      </c>
+          <t>Excelente – Excelencia</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr"/>
       <c r="F101" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12478,25 +12594,29 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Requerimientos de recursos humanos</t>
+          <t>como mínimo tres (3) veces al año</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 9. Requerimientos de recursos humanos</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr"/>
+          <t>como mínimo cuatro (4) veces al año, cada convocatoria en tres (3) semanas continuas, una por ciclo</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
+        </is>
+      </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12507,25 +12627,29 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 12. Ejecución presupuestaria de gastos, 2020 a 2026</t>
+          <t>24 horas de anticipación al examen.</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 10. Ejecución presupuestaria de gastos, 2020 a 2026</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr"/>
+          <t>24 horas de anticipación al examen. El postulante debe aprobar los tres ciclos en un plazo máximo de doce (12) meses calendario desde su inscripción al primer ciclo, y quien repruebe tres (3) veces un mismo ciclo queda inhabilitado para esta modalidad, conforme a los Artículos 60 a 67 del Reglamento de Modalidades de Graduación.</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
+        </is>
+      </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12536,25 +12660,29 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 13. Fuentes de financiamiento complementario</t>
+          <t>Ciclo Servicios</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Fuentes de financiamiento complementario</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr"/>
+          <t>Ciclo de Servicios</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Ciclo Servicios de Aseguramiento</t>
+        </is>
+      </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12565,22 +12693,22 @@
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 14. Fases de implementación</t>
+          <t>Haber aprobado el 100% de las 43 asignaturas en primera instancia (sin haber recurrido a exámenes de mesa ni haber reprobado ninguna materia).</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 12. Fases de implementación</t>
+          <t>Haber aprobado el 100% de las 43 asignaturas en evaluaciones ordinarias de primera instancia, sin haber reprobado, abandonado ni cursado asignaturas en segundo turno, exámenes extraordinarios de mesa o cursos de verano destinados a subsanar reprobaciones.</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr"/>
@@ -12594,22 +12722,22 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 15. Riesgos de implementación y medidas de mitigación</t>
+          <t>Haber concluido el plan de estudios dentro del tiempo reglamentario de la carrera (5 años continuos).</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 13. Riesgos de implementación y medidas de mitigación</t>
+          <t>Haber concluido el plan de estudios en el tiempo reglamentario de cinco (5) gestiones académicas anuales continuas, sin suspensiones voluntarias, abandonos temporales ni postergaciones de matrícula.</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr"/>
@@ -12623,29 +12751,25 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>especifico de un aula</t>
+          <t>Acreditar un promedio general ponderado cuantitativo sobresaliente (igual o superior al límite fijado por la normativa de la Facultad y la UMSA).</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>específico de un aula</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Equipamiento especifico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
-        </is>
-      </c>
+          <t>Acreditar un Promedio Ponderado Acumulado (PPA) igual o superior a setenta y cinco (75) puntos a lo largo de los cinco años de estudio, conforme al Artículo 72 del Reglamento de Modalidades de Graduación.</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr"/>
       <c r="F107" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12656,29 +12780,21 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>clases hibridas</t>
-        </is>
-      </c>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72, requisito agregado)</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr"/>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>clases híbridas</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Equipamiento específico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
-        </is>
-      </c>
+          <t>No registrar antecedentes disciplinarios, sanciones administrativas, procesos en Tribunal de Honor ni fallos de ética universitaria o de plagio académico.</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr"/>
       <c r="F108" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12689,27 +12805,27 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 78)</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>el estudiante de Quinto Año o egresado puede cursar</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>el estudiante que concluyó y aprobó las 43 asignaturas del plan de estudios puede cursar</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Dotación de software de acuerdo a las necesidades del itinerario formativo, por ejemplo: Software de auditoria, Gestores</t>
+          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
@@ -12722,27 +12838,27 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliografico</t>
+          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa).</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliográfico</t>
+          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa). Los programas duran entre cuatro (4) y seis (6) meses y exigen un 80 % de asistencia y una nota mínima de setenta y uno (71) puntos por módulo y en el trabajo final, conforme a los Artículos 77 a 82 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliografico</t>
+          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
@@ -12755,29 +12871,25 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Comentario eliminado</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Herramientas Digitales</t>
+          <t>Comentario de Carlos Gonzales Alanes: "Revisar los nombres de las asignaturas por favor"</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Tecnologías de Información y Herramientas Digitales</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>CPA-102 Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contaduría Pública / Auditoría con Tí</t>
-        </is>
-      </c>
+          <t>Eliminado tras ajustar los nombres a la malla</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12788,7 +12900,7 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -12798,17 +12910,17 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Sistemas ERP y Analítica</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Sistemas Contables ERP y Análisis de Datos</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>CPA-102 Tecnologías de Información y Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contadur</t>
+          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
@@ -12821,27 +12933,27 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Métodos de Investigación</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Métodos y Técnicas de Investigación</t>
+          <t>Técnico Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>CPA-204 Métodos de Investigación: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional de Con</t>
+          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
@@ -12854,27 +12966,27 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Digital y Ciberseguridad</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Digital, Ciberseguridad y Tecnologías Emergentes</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>CPA-505 Auditoría Digital y Ciberseguridad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacio</t>
+          <t>b. Técnico Universitario Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
@@ -12887,29 +12999,25 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Descripción del grado intermedio TUM</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Reportes y Aseguramiento de Sostenibilidad</t>
+          <t xml:space="preserve">a. Técnico Universitario Medio. Conforme al Artículo Segundo de la Resolución HCU N.º 426/2024, el requisito ineludible para extender el Diploma Académico y el Título Profesional de Técnico Universitario Medio es la aprobación de todas las asignaturas de primero y segundo año en el tiempo determinado de dos años, inexcusablemente. </t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Reportes y Aseguramiento de Sostenibilidad y Auditoría Ambiental</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>CPA-506 Reportes y Aseguramiento de Sostenibilidad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisi</t>
-        </is>
-      </c>
+          <t>a. Técnico Universitario Medio. Salida intermedia que conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12920,27 +13028,27 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Peritajes</t>
+          <t>se aprueba con nota mínima de 51 puntos sobre 100.</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>se aprueba con nota mínima de 51 puntos sobre 100. La prueba es escrita, de resolución de casos sobre información financiera, con una duración de noventa (90) minutos, conforme a los Artículos 87 a 90 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>CPA-508 Auditoría Forense y Peritajes: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional d</t>
+          <t>b. Técnico Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de grado técnico</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
@@ -12953,7 +13061,7 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>6.2.2</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
@@ -12963,17 +13071,17 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Contador Publico</t>
+          <t xml:space="preserve">digital,  </t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Contador Público</t>
+          <t>digital,</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+          <t xml:space="preserve">Promover nuevos campos de investigación científica, especialmente aquellos que contribuyan a la construcción teórica de </t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
@@ -12986,29 +13094,25 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Contenido duplicado eliminado</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>7.2Políticas y líneas de extensión universitaria | 7.2.1Políticas | Educación continua. La Carrera ofrece programas para diversos públicos interesados en las ares contables y financieras que son temas transversales para la gestión. | Articulación con el postgrado. La oferta de extensión se articula con la Unidad de Postgrado y con la modalidad de graduación mediante diplomado del punto 5.4.2. | Di</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
-        </is>
-      </c>
+          <t>Se conserva la segunda versión de 7.2 y 7.2.1, que contiene y amplía todos los ítems de la primera</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13019,27 +13123,27 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>12.1.2</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>12.1.3Componentes de la evaluación</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr">
@@ -13052,27 +13156,27 @@
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>12.1.5Dimensiones de la evaluación del plan de estudios</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
@@ -13085,27 +13189,27 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>12.1.4</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>12.1.6Seguimiento del desarrollo curricular</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
@@ -13118,27 +13222,27 @@
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>12.1.7</t>
+          <t>Auditoría de Proyectos Público y Privado</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>12.1.7Mecanismos de seguimiento anual</t>
+          <t>Auditoría de Proyectos Público y Privado</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
@@ -13151,27 +13255,27 @@
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>12.1.9</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>12.1.9Evaluación del plan al concluir su implementación</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
@@ -13184,29 +13288,25 @@
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>12.1.10</t>
+          <t>Cuadro 5. Estudiantes inscritos por asignatura y paralelo</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>12.1.7</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>12.1.10Responsables y uso de los resultados</t>
-        </is>
-      </c>
+          <t>Cuadro 6. Estudiantes inscritos por asignatura y paralelo</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13217,27 +13317,27 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>estudiantes  por</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>estudiantes por</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Tasa de egreso en los cinco años previstos y con uno o dos años de rezago; tasa de titulación por cohorte; retención y a</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr">
@@ -13250,27 +13350,27 @@
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>13.1.2</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Referencia cruzada</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Puntos 4.7.5 y 5.3</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Puntos 5.3.3 y 5.3.4</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Puntos 4.7.5 y 5.3</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
@@ -13283,27 +13383,27 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Referencia cruzada</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>conforme al punto 4.7.5.</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>conforme al punto 5.3.4.</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las mesas de examen se rigen por la Resolución HCU N.º 352/2021, cuyo Artículo 8 las limita a las materias teóricas del </t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
@@ -13316,27 +13416,27 @@
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Él o los Docentes</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>El o los Docentes</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>4 vez/veces</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
@@ -13349,27 +13449,27 @@
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>la División, de Gestiones</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>la División de Gestiones</t>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>1 vez/veces</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
@@ -13382,27 +13482,27 @@
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencia Económicas</t>
+          <t>Contaduría Publica</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas</t>
+          <t>Contaduría Pública</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>1 vez/veces</t>
+          <t>La Carrera de Contaduría Publica actualmente cuenta con la siguiente bibliografía:</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
@@ -13415,29 +13515,25 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>expedido la Unidad</t>
+          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.143 estudiantes inscritos en 2025. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>expedido por la Unidad</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.116 estudiantes inscritos en 2026. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13448,29 +13544,25 @@
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>En caso, de no existir</t>
+          <t>Cuadro 11. Requerimientos de recursos humanos</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>En caso de no existir</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Cuadro 9. Requerimientos de recursos humanos</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13481,29 +13573,25 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>veintiún 21)</t>
+          <t>Cuadro 12. Ejecución presupuestaria de gastos, 2020 a 2026</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>veintiún (21)</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Cuadro 10. Ejecución presupuestaria de gastos, 2020 a 2026</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13514,29 +13602,25 @@
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Kardex Académico:  Expedido</t>
+          <t>Cuadro 13. Fuentes de financiamiento complementario</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Kardex Académico: Expedido</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Cuadro 11. Fuentes de financiamiento complementario</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr"/>
       <c r="F134" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13547,29 +13631,25 @@
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas, a lo largo</t>
+          <t>Cuadro 14. Fases de implementación</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas), a lo largo</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Cuadro 12. Fases de implementación</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13580,29 +13660,25 @@
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior – Contador General</t>
+          <t>Cuadro 15. Riesgos de implementación y medidas de mitigación</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior – Contador General)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Cuadro 13. Riesgos de implementación y medidas de mitigación</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13613,29 +13689,21 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>Auxiliar en Contabilidad General</t>
-        </is>
-      </c>
+          <t>Datos de matrícula, gestión 2026</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr"/>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Auxiliar Contable</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr"/>
       <c r="F137" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13646,29 +13714,25 @@
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>Presupuestos y Contabilidad Gubernamental (CPA-304)</t>
+          <t xml:space="preserve">Entre 2021 y 2025, los estudiantes matriculados disminuyeron en 8,97 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental (CPA-304)</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr"/>
       <c r="F138" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13679,29 +13743,25 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr"/>
       <c r="F139" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13712,29 +13772,25 @@
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos (CPA-408)</t>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo (CPA-408)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.180, todavía representa </t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13745,29 +13801,25 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.3</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos: Público y Privado (CPA-507)</t>
+          <t>4.283 matriculados y 3.143 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos (CPA-507)</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>4.296 matriculados y 3.116 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13778,27 +13830,27 @@
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras (CPA-509)</t>
+          <t>especifico de un aula</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras y Servicios Relacionados (CPA-509)</t>
+          <t>específico de un aula</t>
         </is>
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>1 vez/veces</t>
+          <t>Equipamiento especifico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
@@ -13811,25 +13863,29 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>Texto anterior del punto 13.1.4 (83 párrafos y tablas: 46 artículos en 6 capítulos)</t>
+          <t>clases hibridas</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Reemplazado por el Reglamento de Modalidades de Graduación íntegro (Capítulos I a X, Artículos 1 a 90 y 87-Bis, Disposiciones Transitorias y Finales), con el formato del documento</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr"/>
+          <t>clases híbridas</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>Equipamiento específico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
+        </is>
+      </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13840,25 +13896,29 @@
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>Párrafos partidos en el original (Art. 47 «, estando obligado…» y ponderación del Art. 55 en cinco líneas)</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Unidos en un solo párrafo cada uno</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr"/>
+          <t>auditoría</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Dotación de software de acuerdo a las necesidades del itinerario formativo, por ejemplo: Software de auditoria, Gestores</t>
+        </is>
+      </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13869,25 +13929,29 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>13.2.2</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
+          <t>Material Bibliografico</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr"/>
+          <t>Material Bibliográfico</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Material Bibliografico</t>
+        </is>
+      </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13898,29 +13962,25 @@
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>11.2.1</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas troncales. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servidores, 10 de planta y 13</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>MAT-201 Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas del Área Contable y de Auditoría. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servid</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr"/>
       <c r="F146" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13931,29 +13991,25 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>11.2.1</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>CPA-304 Contabilidad y Presupuestos Gubernamental</t>
-        </is>
-      </c>
+          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr"/>
       <c r="F147" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13964,7 +14020,7 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -13974,17 +14030,17 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Herramientas Digitales</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Tecnologías de Información y Herramientas Digitales</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>CPA-408 Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>CPA-102 Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contaduría Pública / Auditoría con Tí</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
@@ -13997,7 +14053,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -14007,17 +14063,17 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Sistemas ERP y Analítica</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Sistemas Contables ERP y Análisis de Datos</t>
         </is>
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>CPA-507 Auditoría de Proyectos Públicos y Privados</t>
+          <t>CPA-102 Tecnologías de Información y Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contadur</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
@@ -14030,7 +14086,7 @@
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -14040,17 +14096,17 @@
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Métodos de Investigación</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Métodos y Técnicas de Investigación</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>CPA-508 Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>CPA-204 Métodos de Investigación: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional de Con</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
@@ -14063,27 +14119,27 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Auditoría Digital y Ciberseguridad</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
+          <t>Auditoría Digital, Ciberseguridad y Tecnologías Emergentes</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Habilitación de la salida intermedia de Técnico Universitario Superior en Contabilidad General; planes de asignatura de </t>
+          <t>CPA-505 Auditoría Digital y Ciberseguridad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacio</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
@@ -14096,39 +14152,2379 @@
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
+          <t>11.2.2</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Reportes y Aseguramiento de Sostenibilidad</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Reportes y Aseguramiento de Sostenibilidad y Auditoría Ambiental</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>CPA-506 Reportes y Aseguramiento de Sostenibilidad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisi</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>11.2.2</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense y Peritajes</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>CPA-508 Auditoría Forense y Peritajes: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional d</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>11.2.2</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>Ortografía</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Contador Publico</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Contador Público</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>11.2.2</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Ortografía</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>11.2.2</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular 2027 y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen los siguientes perfi</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular del Rediseño Curricular y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen l</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr"/>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>11.3.1</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>Para evaluar la capacidad financiera que respaldará la implementación del Plan 2027, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>Para evaluar la capacidad financiera que respaldará la implementación del Rediseño Curricular, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr"/>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>11.3.2</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Plan 2027 se rige por los siguiente</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Rediseño Curricular se rige por los</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr"/>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>12.1.3</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>12.1.2</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>12.1.3Componentes de la evaluación</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>12.1.5</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>12.1.3</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>12.1.5Dimensiones de la evaluación del plan de estudios</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>12.1.6</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>12.1.4</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>12.1.6Seguimiento del desarrollo curricular</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>12.1.7</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>12.1.5</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>12.1.7Mecanismos de seguimiento anual</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>12.1.9</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>12.1.6</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>12.1.9Evaluación del plan al concluir su implementación</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de subpuntos</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>12.1.10</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>12.1.7</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>12.1.10Responsables y uso de los resultados</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>12.1.3</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Ortografía</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>estudiantes  por</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>estudiantes por</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>Tasa de egreso en los cinco años previstos y con uno o dos años de rezago; tasa de titulación por cohorte; retención y a</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>Este punto identifica la normativa universitaria que rige el Plan de Estudios 2027, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del I</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>Este punto identifica la normativa universitaria que rige el Rediseño Curricular, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del Ins</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr"/>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>13.1.1</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 1. Normativa universitaria aplicable al Plan 2027</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 1. Normativa universitaria aplicable al Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr"/>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>13.1.2</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>Referencia cruzada</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Puntos 4.7.5 y 5.3</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Puntos 5.3.3 y 5.3.4</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>Puntos 4.7.5 y 5.3</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>13.1.2</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>La implementación del Plan 2027 requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a partir de la Re</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>La implementación del Rediseño Curricular requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a parti</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>13.1.2</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 2. Reglamentos internos para la implementación del Plan 2027</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 2. Reglamentos internos para la implementación del Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>13.1.3</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Referencia cruzada</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>conforme al punto 4.7.5.</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>conforme al punto 5.3.4.</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las mesas de examen se rigen por la Resolución HCU N.º 352/2021, cuyo Artículo 8 las limita a las materias teóricas del </t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>13.1.3</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>13.1.3</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>Término: Área Contable y de Auditoría y Área Contextual</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr"/>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr"/>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>De conformidad con el Plan de Estudios 2027 y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>De conformidad con el Rediseño Curricular y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr"/>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Plan de Estudios 2027, se reconocen oficialmente las siguientes modalidades:</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Rediseño Curricular, se reconocen oficialmente las siguientes modalidades:</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>Término: Área Contable y de Auditoría</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas troncales del ciclo intermedio (Primer a Tercer año).</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas del Área Contable y de Auditoría del ciclo intermedio (Primer a Tercer año).</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr"/>
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>Término: Contador Público</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Él o los Docentes</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>El o los Docentes</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>4 vez/veces</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>la División, de Gestiones</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>la División de Gestiones</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>Facultad de Ciencia Económicas</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>Facultad de Ciencias Económicas</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>expedido la Unidad</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>expedido por la Unidad</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>En caso, de no existir</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>En caso de no existir</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>veintiún 21)</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>veintiún (21)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>Kardex Académico:  Expedido</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Kardex Académico: Expedido</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>Facultad de Ciencias Económicas, a lo largo</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Facultad de Ciencias Económicas), a lo largo</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Superior – Contador General</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Superior – Contador General)</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>Auxiliar en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Auxiliar Contable</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>Presupuestos y Contabilidad Gubernamental (CPA-304)</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Presupuesto y Contabilidad Gubernamental (CPA-304)</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F191" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos (CPA-408)</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo (CPA-408)</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Proyectos: Público y Privado (CPA-507)</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos (CPA-507)</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F193" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Entidades Financieras (CPA-509)</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Entidades Financieras y Servicios Relacionados (CPA-509)</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>Texto anterior del punto 13.1.4 (83 párrafos y tablas: 46 artículos en 6 capítulos)</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>Reemplazado por el Reglamento de Modalidades de Graduación íntegro (Capítulos I a X, Artículos 1 a 90 y 87-Bis, Disposiciones Transitorias y Finales), con el formato del documento</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr"/>
+      <c r="F195" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>13.1.4</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>Reglamento de Modalidades de Graduación</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>Párrafos partidos en el original (Art. 47 «, estando obligado…» y ponderación del Art. 55 en cinco líneas)</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>Unidos en un solo párrafo cada uno</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr"/>
+      <c r="F196" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>13.2.2</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>Numeración de cuadros</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 6. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 3. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr"/>
+      <c r="F197" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>13.2.2</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>El reglamento interno del Instituto se actualizará para articularlo con el Plan 2027 con base en los siguientes lineamientos:</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>El reglamento interno del Instituto se actualizará para articularlo con el Rediseño Curricular con base en los siguientes lineamientos:</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr"/>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>Datos de matrícula, gestión 2026</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.143 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.116 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr"/>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t>14.9.1</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>Datos de matrícula, gestión 2026</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>Frente a 4.283 estudiantes matriculados y 3.143 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>Frente a 4.296 estudiantes matriculados y 3.116 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr"/>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Plan de Estudios 2027: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementac</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Rediseño Curricular: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementació</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr"/>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>16.1.1</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Plan 2027 mediante homologación o convalidación.</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Rediseño Curricular mediante homologación o convalidación.</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr"/>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G202" s="10" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>16.1.1</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Plan 2027.</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Rediseño Curricular.</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr"/>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G203" s="10" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>16.1.1</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>Implantación gradual. El Plan 2027 se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Implantación gradual. El Rediseño Curricular se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr"/>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>MAT-201 Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+        </is>
+      </c>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G205" s="10" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>CPA-304 Contabilidad y Presupuestos Gubernamental</t>
+        </is>
+      </c>
+      <c r="F206" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>CPA-408 Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+        </is>
+      </c>
+      <c r="F207" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G207" s="10" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>CPA-507 Auditoría de Proyectos Públicos y Privados</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G208" s="10" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de asignatura (malla definitiva)</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>CPA-508 Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G209" s="10" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr"/>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G210" s="10" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Plan 2027:</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Rediseño Curricular:</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr"/>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G211" s="10" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Plan de Estudios 2027</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr"/>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G212" s="10" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>Asignatura equivalente del Plan 2027</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>Asignatura equivalente del Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr"/>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G213" s="10" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Plan 2027.</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Rediseño Curricular.</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr"/>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G214" s="10" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr"/>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G215" s="10" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>16.1.3</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t>Fuente: elaboración con base en la malla curricular 2027 y en la propuesta de equivalencias de la Carrera.</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>Fuente: elaboración con base en la malla curricular del Rediseño Curricular y en la propuesta de equivalencias de la Carrera.</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr"/>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>16.1.4</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C217" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Plan 2027 en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Rediseño Curricular en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr"/>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G217" s="10" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>16.1.4</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Plan 2027 que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Rediseño Curricular que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr"/>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G218" s="10" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>16.1.4</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Plan 2027. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de actualizació</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Rediseño Curricular. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de ac</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr"/>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G219" s="10" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
           <t>16.2</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Habilitación de la salida intermedia de Técnico Universitario Superior en Contabilidad General; planes de asignatura de </t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G220" s="10" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t>Referencia cruzada</t>
         </is>
       </c>
-      <c r="C152" s="7" t="inlineStr">
+      <c r="C221" s="7" t="inlineStr">
         <is>
           <t>12.1.5.</t>
         </is>
       </c>
-      <c r="D152" s="7" t="inlineStr">
+      <c r="D221" s="7" t="inlineStr">
         <is>
           <t>12.1.3.</t>
         </is>
       </c>
-      <c r="E152" s="7" t="inlineStr">
+      <c r="E221" s="7" t="inlineStr">
         <is>
           <t>Fuente: elaboración con base en los puntos 11.3.4 y 12.1.5.</t>
         </is>
       </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>En proceso</t>
-        </is>
-      </c>
-      <c r="G152" s="10" t="n"/>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G221" s="10" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 2. Cronograma de implementación del Plan 2027</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 2. Cronograma de implementación del Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr"/>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G222" s="10" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>Plan de Estudios 2027</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr"/>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G223" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
+        <is>
+          <t>Primera promoción del Plan 2027</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>Primera promoción del Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr"/>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G224" s="10" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Plan 2027, el Honorable </t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Rediseño Curricular, el </t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr"/>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G225" s="10" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
+        <is>
+          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Plan 2027 ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Rediseño Curricular ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr"/>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G226" s="10" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C227" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Plan 2027, con reconocimiento en su historial académico.</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Rediseño Curricular, con reconocimiento en su historial académico.</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr"/>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G227" s="10" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Plan 2027 o el PETAENG, conforme al punto 13.1.4.</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Rediseño Curricular o el PETAENG, conforme al punto 13.1.4.</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr"/>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G228" s="10" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G152"/>
-  <conditionalFormatting sqref="F4:F152">
+  <autoFilter ref="A3:G228"/>
+  <conditionalFormatting sqref="F4:F228">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F4="Corregido"</formula>
     </cfRule>
@@ -14143,7 +16539,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F4:F152" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F228" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En proceso,Corregido,No aplica"</formula1>
     </dataValidation>
   </dataValidations>

--- a/rediseno_2026/Documento unificado/Revisión del documento unificado - calificación HCU 32-2025, términos y correcciones.xlsx
+++ b/rediseno_2026/Documento unificado/Revisión del documento unificado - calificación HCU 32-2025, términos y correcciones.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requisitos'!$A$3:$I$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Puntos'!$A$3:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Términos'!$A$3:$I$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correcciones'!$A$3:$G$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correcciones'!$A$3:$G$233</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Coherencia'!$A$3:$H$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9566,7 +9566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9693,7 +9693,7 @@
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Se agregó el Índice (hasta el nivel 1.1.1) y el Índice de cuadros agrupado por punto, como campos de Word que se actualizan al abrir el archivo.</t>
+          <t>Se agregó el Índice (hasta el nivel 1.1.1) y el Índice de cuadros agrupado por punto. Para recalcular las páginas en Word: clic derecho sobre cada índice, Actualizar campos, Actualizar toda la tabla.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -9718,7 +9718,7 @@
       <c r="C7" s="7" t="inlineStr"/>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Numeración de páginas continua: se quitó el reinicio en 1 de las 21 secciones.</t>
+          <t>Se quitaron los resaltados de revisión (10.12 y 13.1.1) y se dejaron los metadatos del archivo con autor Carrera de Contaduría Pública - UMSA, sin marcas de herramientas de edición.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -9743,7 +9743,7 @@
       <c r="C8" s="7" t="inlineStr"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Los títulos numerados tienen nivel de esquema (aparecen en el panel de navegación de Word) y los títulos de cuadro usan el estilo TituloCuadro.</t>
+          <t>Numeración de páginas continua: se quitó el reinicio en 1 de las 21 secciones.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -9757,29 +9757,21 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
-        </is>
-      </c>
+          <t>Estructura y formato</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>La Resolución del Honorable Consejo Universitario N.º 290/2016 aprueba la denominación de Técnico Universitario Superior</t>
-        </is>
-      </c>
+          <t>Los títulos numerados tienen nivel de esquema (aparecen en el panel de navegación de Word) y los títulos de cuadro usan el estilo TituloCuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -9810,7 +9802,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>La Resolución del Honorable Consejo Universitario N.º 290/2016 aprueba la denominación de Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -9828,20 +9820,24 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Descripción del grado intermedio TUM</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al concluir el segundo año de formación académica, el estudiante puede acceder además al grado de Técnico Universitario Medio en Contabilidad. La Resolución del Honorable Consejo Universitario N.º 426/2024, de 24 de julio de 2024, incluye este grado en el Cuadro General de Grados de la UMSA y establece que el requisito ineludible para la extensión del Diploma Académico y del Título Profesional de </t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Salida Intermedia Técnico Universitario Medio: Conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumpli</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
+          <t>Técnico Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
+        </is>
+      </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -9852,29 +9848,25 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Descripción del grado intermedio TUM</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t xml:space="preserve">Al concluir el segundo año de formación académica, el estudiante puede acceder además al grado de Técnico Universitario Medio en Contabilidad. La Resolución del Honorable Consejo Universitario N.º 426/2024, de 24 de julio de 2024, incluye este grado en el Cuadro General de Grados de la UMSA y establece que el requisito ineludible para la extensión del Diploma Académico y del Título Profesional de </t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior en Contabilidad General, conforme a la Resolución del Honorable Consejo Universitario N.º</t>
-        </is>
-      </c>
+          <t>Salida Intermedia Técnico Universitario Medio: Conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumpli</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -9885,25 +9877,29 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Personal administrativo de planta</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1. Personal administrativo de planta</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
+          <t>Técnico Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Universitario Superior en Contabilidad General, conforme a la Resolución del Honorable Consejo Universitario N.º</t>
+        </is>
+      </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -9924,12 +9920,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 4. Personal administrativo a contrato</t>
+          <t>Cuadro 3. Personal administrativo de planta</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 2. Personal administrativo a contrato</t>
+          <t>Cuadro 1. Personal administrativo de planta</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -9953,12 +9949,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5. Personal de las unidades dependientes de la Carrera</t>
+          <t>Cuadro 4. Personal administrativo a contrato</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Personal de las unidades dependientes de la Carrera</t>
+          <t>Cuadro 2. Personal administrativo a contrato</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -9982,12 +9978,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Docentes por categoría</t>
+          <t>Cuadro 5. Personal de las unidades dependientes de la Carrera</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 4. Docentes por categoría</t>
+          <t>Cuadro 3. Personal de las unidades dependientes de la Carrera</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -10011,12 +10007,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 7. Carga horaria de los docentes por áreas, expresada en cantidad de docentes</t>
+          <t>Cuadro 6. Docentes por categoría</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5. Carga horaria de los docentes por áreas, expresada en cantidad de docentes</t>
+          <t>Cuadro 4. Docentes por categoría</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -10040,12 +10036,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 8. Docentes sin duplicidad entre áreas</t>
+          <t>Cuadro 7. Carga horaria de los docentes por áreas, expresada en cantidad de docentes</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Docentes sin duplicidad entre áreas</t>
+          <t>Cuadro 5. Carga horaria de los docentes por áreas, expresada en cantidad de docentes</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -10069,12 +10065,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Sumatoria total según el Cuadro 7</t>
+          <t>Cuadro 8. Docentes sin duplicidad entre áreas</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Sumatoria total según el Cuadro 5</t>
+          <t>Cuadro 6. Docentes sin duplicidad entre áreas</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -10098,12 +10094,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Los Cuadros 7 y 8 permiten establecer lo siguiente:</t>
+          <t>Sumatoria total según el Cuadro 7</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Los Cuadros 5 y 6 permiten establecer lo siguiente:</t>
+          <t>Sumatoria total según el Cuadro 5</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -10127,12 +10123,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 9. Docentes por áreas y categoría, expresado en cantidad de asignaturas</t>
+          <t>Los Cuadros 7 y 8 permiten establecer lo siguiente:</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 7. Docentes por áreas y categoría, expresado en cantidad de asignaturas</t>
+          <t>Los Cuadros 5 y 6 permiten establecer lo siguiente:</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
@@ -10156,12 +10152,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 10. Docentes por áreas y categoría, expresado en porcentaje</t>
+          <t>Cuadro 9. Docentes por áreas y categoría, expresado en cantidad de asignaturas</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 8. Docentes por áreas y categoría, expresado en porcentaje</t>
+          <t>Cuadro 7. Docentes por áreas y categoría, expresado en cantidad de asignaturas</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
@@ -10185,12 +10181,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Fuente: elaboración propia con base en el Cuadro 9.</t>
+          <t>Cuadro 10. Docentes por áreas y categoría, expresado en porcentaje</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Fuente: elaboración propia con base en el Cuadro 7.</t>
+          <t>Cuadro 8. Docentes por áreas y categoría, expresado en porcentaje</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
@@ -10214,12 +10210,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Según los Cuadros 9 y 10, existen 85 designaciones de docentes titulares, equivalentes al 46,45 %, y 98 de docentes inte</t>
+          <t>Fuente: elaboración propia con base en el Cuadro 9.</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Según los Cuadros 7 y 8, existen 85 designaciones de docentes titulares, equivalentes al 46,45 %, y 98 de docentes inter</t>
+          <t>Fuente: elaboración propia con base en el Cuadro 7.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
@@ -10243,12 +10239,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Estudiantes matriculados e inscritos</t>
+          <t>Según los Cuadros 9 y 10, existen 85 designaciones de docentes titulares, equivalentes al 46,45 %, y 98 de docentes inte</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 9. Estudiantes matriculados e inscritos</t>
+          <t>Según los Cuadros 7 y 8, existen 85 designaciones de docentes titulares, equivalentes al 46,45 %, y 98 de docentes inter</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -10272,12 +10268,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Del Cuadro 11 se establece lo siguiente:</t>
+          <t>Cuadro 11. Estudiantes matriculados e inscritos</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Del Cuadro 9 se establece lo siguiente:</t>
+          <t>Cuadro 9. Estudiantes matriculados e inscritos</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
@@ -10301,12 +10297,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Las cifras de inscritos del Cuadro 11 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes des</t>
+          <t>Del Cuadro 11 se establece lo siguiente:</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desc</t>
+          <t>Del Cuadro 9 se establece lo siguiente:</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr"/>
@@ -10330,12 +10326,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 12. Estudiantes titulados por modalidad de graduación</t>
+          <t>Las cifras de inscritos del Cuadro 11 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes des</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 10. Estudiantes titulados por modalidad de graduación</t>
+          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desc</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr"/>
@@ -10359,12 +10355,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Según el Cuadro 12, la mayoría de los estudiantes se titula mediante el examen de grado, que en el periodo 2021 a 2025 r</t>
+          <t>Cuadro 12. Estudiantes titulados por modalidad de graduación</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Según el Cuadro 10, la mayoría de los estudiantes se titula mediante el examen de grado, que en el periodo 2021 a 2025 r</t>
+          <t>Cuadro 10. Estudiantes titulados por modalidad de graduación</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr"/>
@@ -10388,12 +10384,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 13. Estudiantes inscritos por asignatura y paralelo</t>
+          <t>Según el Cuadro 12, la mayoría de los estudiantes se titula mediante el examen de grado, que en el periodo 2021 a 2025 r</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Estudiantes inscritos por asignatura y paralelo</t>
+          <t>Según el Cuadro 10, la mayoría de los estudiantes se titula mediante el examen de grado, que en el periodo 2021 a 2025 r</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr"/>
@@ -10417,12 +10413,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Según el Cuadro 13, el promedio de estudiantes por paralelo se mantiene entre 104 y 109 en el periodo 2023 a 2026, una c</t>
+          <t>Cuadro 13. Estudiantes inscritos por asignatura y paralelo</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Según el Cuadro 11, el promedio de estudiantes por paralelo se mantiene entre 104 y 109 en el periodo 2023 a 2026, una c</t>
+          <t>Cuadro 11. Estudiantes inscritos por asignatura y paralelo</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr"/>
@@ -10436,29 +10432,25 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Según el Cuadro 13, el promedio de estudiantes por paralelo se mantiene entre 104 y 109 en el periodo 2023 a 2026, una c</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior en Contabilidad General y título en provisión nacional de Contador General; Técnico Unive</t>
-        </is>
-      </c>
+          <t>Según el Cuadro 11, el promedio de estudiantes por paralelo se mantiene entre 104 y 109 en el periodo 2023 a 2026, una c</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10474,22 +10466,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>titulo en provisión</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>título en provisión</t>
+          <t>Técnico Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General y título en provisión nacional de Contador General; Técnico Universitario Medio</t>
+          <t>Técnico Universitario Superior en Contabilidad General y título en provisión nacional de Contador General; Técnico Unive</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
@@ -10507,20 +10499,24 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Estudiantes matriculados, gestión 2025</t>
+          <t>titulo en provisión</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Estudiantes matriculados, gestión 2026</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
+          <t>título en provisión</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Superior en Contabilidad General y título en provisión nacional de Contador General; Técnico Universitario Medio</t>
+        </is>
+      </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10541,12 +10537,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>4.283</t>
+          <t>Estudiantes matriculados, gestión 2025</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>4.296: 3.743 antiguos y 553 nuevos, en la sede de La Paz</t>
+          <t>Estudiantes matriculados, gestión 2026</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr"/>
@@ -10570,12 +10566,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Estudiantes inscritos, gestión 2025</t>
+          <t>4.283</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Estudiantes inscritos, gestión 2026</t>
+          <t>4.296: 3.743 antiguos y 553 nuevos, en la sede de La Paz</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr"/>
@@ -10599,12 +10595,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>3.247: 3.143 en la sede de La Paz y 104 en las sedes desconcentradas</t>
+          <t>Estudiantes inscritos, gestión 2025</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>3.116 en la sede de La Paz; las sedes desconcentradas registraron 104 inscritos en 2025</t>
+          <t>Estudiantes inscritos, gestión 2026</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr"/>
@@ -10618,29 +10614,25 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Contaduría publica</t>
+          <t>3.247: 3.143 en la sede de La Paz y 104 en las sedes desconcentradas</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Pública</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El Plan Estratégico Institucional de la Carrera de Contaduría publica forma parte del plan estratégico Institucional de </t>
-        </is>
-      </c>
+          <t>3.116 en la sede de La Paz; las sedes desconcentradas registraron 104 inscritos en 2025</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr"/>
       <c r="F38" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10651,7 +10643,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -10661,17 +10653,17 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>kardixtas</t>
+          <t>Contaduría publica</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>kardexistas</t>
+          <t>Contaduría Pública</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Apoyo académico y administrativo: Encargado de Kárdex, con una encargada de Kárdex I y dos kardixtas académicos; dos enc</t>
+          <t xml:space="preserve">El Plan Estratégico Institucional de la Carrera de Contaduría publica forma parte del plan estratégico Institucional de </t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -10684,25 +10676,29 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>2.6.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Con una población de 4.283 estudiantes matriculados y 3.143 inscritos en la gestión 2025, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
+          <t>kardixtas</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Con una población de 4.296 estudiantes matriculados y 3.116 inscritos en la gestión 2026, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr"/>
+          <t>kardexistas</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Apoyo académico y administrativo: Encargado de Kárdex, con una encargada de Kárdex I y dos kardixtas académicos; dos enc</t>
+        </is>
+      </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10713,29 +10709,25 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2.7.1</t>
+          <t>2.6.1</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Con una población de 4.283 estudiantes matriculados y 3.143 inscritos en la gestión 2025, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Área Contable y de Auditoria</t>
-        </is>
-      </c>
+          <t>Con una población de 4.296 estudiantes matriculados y 3.116 inscritos en la gestión 2026, el personal administrativo disponible permite atender la demanda académica y administrativa, aunque esa capacidad se sostiene principalmente con personal contratado. El funcionamiento adecuado de la Carrera dep</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -10766,7 +10758,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Total Área Contable y de Auditoria</t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -10789,17 +10781,17 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>El área contable y de auditoria concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de</t>
+          <t>Total Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -10822,17 +10814,17 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>auditoría</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Área Contable y de Auditoria</t>
+          <t>El área contable y de auditoria concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -10865,7 +10857,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Total Área Contable y de Auditoria</t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -10898,7 +10890,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Área Contable y de Auditoria</t>
+          <t>Total Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -10931,7 +10923,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Total Área Contable y de Auditoria</t>
+          <t>Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -10954,17 +10946,17 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de</t>
+          <t>Total Área Contable y de Auditoria</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -10982,20 +10974,24 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contextual</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>El área contable y de auditoría concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>El área contable y de auditoría concentran 73 cargas horarias y el Área Contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr"/>
+          <t>auditoría</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de</t>
+        </is>
+      </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11016,12 +11012,12 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
+          <t>El área contable y de auditoría concentran 73 cargas horarias y el área contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
+          <t>El área contable y de auditoría concentran 73 cargas horarias y el Área Contextual 35, lo que refleja la distribución de las asignaturas por áreas.</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr"/>
@@ -11035,18 +11031,22 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2.7.2</t>
+          <t>2.7.1</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr"/>
+          <t>Término: Área Contextual</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
+        </is>
+      </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
+          <t>Como apoyo a la docencia, durante las gestiones 2023 a 2026 la Carrera contó con una asignación constante de 79 ítems de auxiliares de docencia, equivalentes a 1.580 horas de apoyo académico por gestión. Estas auxiliaturas priorizan las asignaturas del área contable y de auditoría; sin embargo, es n</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
@@ -11068,14 +11068,10 @@
           <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.283 en 2025, lo que representa una reducción del 8,97 %.</t>
-        </is>
-      </c>
+      <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.296 en 2026, lo que representa una reducción del 8,69 %.</t>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr"/>
@@ -11099,12 +11095,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.143, equivalente a una disminución del 0,29 %.</t>
+          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.283 en 2025, lo que representa una reducción del 8,97 %.</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.116, equivalente a una disminución del 1,14 %.</t>
+          <t>Los estudiantes matriculados disminuyeron de 4.705 en 2021, año base, a 4.296 en 2026, lo que representa una reducción del 8,69 %.</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr"/>
@@ -11128,12 +11124,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.140 en 2025, que representan el 26,62 % del total de matriculados.</t>
+          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.143, equivalente a una disminución del 0,29 %.</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.180 en 2026, aunque aumentó respecto de los 1.140 de 2025, y representa el 27,47 % del total de matriculados.</t>
+          <t>Los estudiantes inscritos se mantuvieron estables en el mismo periodo, con una variación de 3.152 a 3.116, equivalente a una disminución del 1,14 %.</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -11157,12 +11153,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
+          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.140 en 2025, que representan el 26,62 % del total de matriculados.</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
+          <t>La diferencia corresponde a estudiantes que obtuvieron su matrícula universitaria pero no se inscribieron en ninguna asignatura durante el año. Esta cifra se redujo de 1.553 en 2021 a 1.180 en 2026, aunque aumentó respecto de los 1.140 de 2025, y representa el 27,47 % del total de matriculados.</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
@@ -11176,22 +11172,22 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>3.1.1</t>
+          <t>2.7.2</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contable y de Auditoría</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son troncales, el 67,</t>
+          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
+          <t>Las cifras de inscritos del Cuadro 9 corresponden a la sede de La Paz. Si se suman los 104 estudiantes de las sedes desconcentradas, la Carrera registró 3.247 inscritos en la gestión 2025, de los cuales 1.830 son mujeres, el 56 %, y 1.417 varones, el 44 %. Además, 1.589 estudiantes, el 48,9 %, reali</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr"/>
@@ -11215,12 +11211,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Subtotal troncal</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son troncales, el 67,</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Subtotal Área Contable y de Auditoría</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr"/>
@@ -11239,17 +11235,17 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contextual</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
+          <t>Subtotal troncal</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
+          <t>Subtotal Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr"/>
@@ -11273,12 +11269,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Subtotal contextual</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Subtotal Área Contextual</t>
+          <t>El Plan de Estudios 2013 fue aprobado por el Primer Congreso Académico de la Carrera y por las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, y rige desde febrero de 2013. Comprende cinco años, 43 asignaturas y 6.000 horas académicas. De las asignaturas, 29 son del Área Contable</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr"/>
@@ -11302,12 +11298,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>La estructura muestra un rasgo que condiciona el rediseño: las áreas contextuales se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación es secuencial</t>
+          <t>Subtotal contextual</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
+          <t>Subtotal Área Contextual</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
@@ -11331,7 +11327,7 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
+          <t>La estructura muestra un rasgo que condiciona el rediseño: las áreas contextuales se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación es secuencial</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -11350,18 +11346,22 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr"/>
+          <t>Término: Área Contextual</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
+        </is>
+      </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180 | 72,53</t>
+          <t xml:space="preserve">La estructura muestra un rasgo que condiciona el rediseño: las asignaturas del Área Contextual se concentran en los tres primeros años y desaparecen en cuarto y quinto, mientras que el bloque de aseguramiento se concentra en los dos últimos años, con 11 de sus 13 asignaturas en quinto. La formación </t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr"/>
@@ -11383,14 +11383,10 @@
           <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2025</t>
-        </is>
-      </c>
+      <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2026</t>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180 | 72,53</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr"/>
@@ -11414,12 +11410,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Matriculados e inscritos, 2025</t>
+          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2025</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Matriculados e inscritos, 2026</t>
+          <t>Cuadro 5. Matrícula e inscripción estudiantil, 2021-2026</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
@@ -11443,12 +11439,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>4.283 y 3.143</t>
+          <t>Matriculados e inscritos, 2025</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>4.296 y 3.116</t>
+          <t>Matriculados e inscritos, 2026</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr"/>
@@ -11472,12 +11468,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>La matrícula cayó 8,97 % desde 2021</t>
+          <t>4.283 y 3.143</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>La matrícula cayó 8,69 % desde 2021</t>
+          <t>4.296 y 3.116</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr"/>
@@ -11501,12 +11497,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>33,01 % en 2021 y 26,62 % en 2025</t>
+          <t>La matrícula cayó 8,97 % desde 2021</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>33,01 % en 2021 y 27,47 % en 2026</t>
+          <t>La matrícula cayó 8,69 % desde 2021</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
@@ -11520,29 +11516,25 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>3.1.2</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>33,01 % en 2021 y 26,62 % en 2025</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y articulación con los diplomados y </t>
-        </is>
-      </c>
+          <t>33,01 % en 2021 y 27,47 % en 2026</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11558,22 +11550,22 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>curgricular</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>curricular</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>El rediseño es el instrumento curgricular para cumplir el OE 1.3 y respalda las metas de acreditación de la Carrera</t>
+          <t xml:space="preserve">Grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y articulación con los diplomados y </t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -11586,7 +11578,7 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
@@ -11596,17 +11588,17 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>curgricular</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
+          <t>curricular</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Aplicaciones para auditoria y finanzas</t>
+          <t>El rediseño es el instrumento curgricular para cumplir el OE 1.3 y respalda las metas de acreditación de la Carrera</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
@@ -11619,25 +11611,29 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Término: Contador Público</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público Autorizado debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y socio</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y sociológicas.</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr"/>
+          <t>auditoría</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Aplicaciones para auditoria y finanzas</t>
+        </is>
+      </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11658,12 +11654,12 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público Autorizado aplica</t>
+          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público Autorizado debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y socio</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público aplica su juicio </t>
+          <t>Lo Multidimensional: Las organizaciones y los seres humanos son unidades complejas multidimensionales. El Contador Público debe reconocer que la información contable no es únicamente cuantitativa-financiera, sino que integra dimensiones éticas, ambientales, tecnológicas, jurídicas y sociológicas.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
@@ -11677,29 +11673,25 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>4.1.4</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Adminisión</t>
+          <t>Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público Autorizado aplica</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Admisión</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>IES 1 Requisitos de Ingreso al Programa: Garantiza la equidad, transparencia y meritocracia en los procesos de selección</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Lo Complejo: Existe complejidad cuando los constituyentes de un todo son inseparables y existe un tejido interdependiente e inter-retroactivo entre el objeto de conocimiento y su entorno. Frente a la incertidumbre y constante evolución del mundo de los negocios, el Contador Público aplica su juicio </t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11710,25 +11702,29 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>4.2.6</t>
+          <t>4.1.4</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Término: Contador Público</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público Autorizado</t>
+          <t>Adminisión</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr"/>
+          <t>Admisión</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>IES 1 Requisitos de Ingreso al Programa: Garantiza la equidad, transparencia y meritocracia en los procesos de selección</t>
+        </is>
+      </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11739,29 +11735,25 @@
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>4.3.2</t>
+          <t>4.2.6</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público Autorizado</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>los grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y la articulación de la graduaci</t>
-        </is>
-      </c>
+          <t>Cuadro 3. Matriz resumen de las competencias del Contador Público</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr"/>
       <c r="F75" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11772,27 +11764,27 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>4.3.4</t>
+          <t>4.3.2</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Sector Publico</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Sector Público</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Incorporar los contenidos emergentes de mayor demanda: Normas del Sector Publico, NIIF y NIIF de Sostenibilidad, asegura</t>
+          <t>los grados intermedios de Técnico Universitario Medio y Técnico Universitario Superior, y la articulación de la graduaci</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
@@ -11805,27 +11797,27 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>4.3.5</t>
+          <t>4.3.4</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Sector Publico</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Sector Público</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>CPA-302 Contabilidad de Costos y Gestión, CPA-305 Sistemas Contables ERP y Análisis de Datos, CPA-406 Ética e Independen</t>
+          <t>Incorporar los contenidos emergentes de mayor demanda: Normas del Sector Publico, NIIF y NIIF de Sostenibilidad, asegura</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
@@ -11848,17 +11840,17 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>CPA-501 Auditoría Operativa, CPA-502 Gabinete de Auditoría Financiera, CPA-504 Auditoría Gubernamental, CPA-508 Auditorí</t>
+          <t>CPA-302 Contabilidad de Costos y Gestión, CPA-305 Sistemas Contables ERP y Análisis de Datos, CPA-406 Ética e Independen</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
@@ -11871,27 +11863,27 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>4.4.1</t>
+          <t>4.3.5</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Área Contable y de Auditoria</t>
+          <t>CPA-501 Auditoría Operativa, CPA-502 Gabinete de Auditoría Financiera, CPA-504 Auditoría Gubernamental, CPA-508 Auditorí</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
@@ -11942,20 +11934,24 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contextual</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr"/>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Área Contable y de Auditoria</t>
+        </is>
+      </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -11976,12 +11972,12 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Área contextual:</t>
+          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Área Contextual:</t>
+          <t xml:space="preserve">De acuerdo con el modelo curricular por competencias del Sistema de la Universidad Boliviana y con la IES 2 de la IFAC, el Rediseño Curricular organiza sus 43 asignaturas en seis áreas de conocimiento agrupadas en dos bloques: el área contable y de auditoría, que forman el núcleo de la profesión, y </t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr"/>
@@ -11995,29 +11991,25 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>4.4.3</t>
+          <t>4.4.1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contextual</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Área contextual:</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>Área Contextual:</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr"/>
       <c r="F83" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12038,17 +12030,17 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
@@ -12071,17 +12063,17 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -12104,17 +12096,17 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
@@ -12137,17 +12129,17 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
@@ -12160,25 +12152,29 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.4.3</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Formato</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Texto en color rojo (Cuadro 4 de mesas, Cuadro 5 de grados, examen por ciclos y listas de ciclos)</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Color automático</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr"/>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12194,13 +12190,17 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Estructura y formato</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr"/>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Texto en color rojo (Cuadro 4 de mesas, Cuadro 5 de grados, examen por ciclos y listas de ciclos)</t>
+        </is>
+      </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Se eliminó el comentario de la Lic. Carlos Gonzales Alanes y el color rojo del punto 5, tras revisar los nombres de las asignaturas.</t>
+          <t>Color automático</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr"/>
@@ -12214,29 +12214,21 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>5.4.1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior</t>
-        </is>
-      </c>
+          <t>Estructura y formato</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Técnico Universitario Superior</t>
-        </is>
-      </c>
+          <t>Se eliminó el comentario de la Lic. Carlos Gonzales Alanes y el color rojo del punto 5, tras revisar los nombres de las asignaturas.</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr"/>
       <c r="F90" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12257,17 +12249,17 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
+          <t>Técnico Superior</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
@@ -12285,20 +12277,24 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Descripción del grado intermedio TUM</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Aprobación de todas las asignaturas del Primer y Segundo año, 16 asignaturas, en el tiempo determinado (dos años continuos bajo modalidad anual)</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumplimiento de la Resolución HCU Nº 426/2024</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr"/>
+          <t>Técnico Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
+        </is>
+      </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12309,29 +12305,25 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>5.4.2</t>
+          <t>5.4.1</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Descripción del grado intermedio TUM</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Presupuestos y Contabilidad Gubernamental</t>
+          <t>Aprobación de todas las asignaturas del Primer y Segundo año, 16 asignaturas, en el tiempo determinado (dos años continuos bajo modalidad anual)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>Presupuestos y Contabilidad Gubernamental</t>
-        </is>
-      </c>
+          <t>Aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto cumplimiento de la Resolución HCU Nº 426/2024</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12352,17 +12344,17 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Presupuestos y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Presupuestos y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
@@ -12385,17 +12377,17 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos: Público y Privado</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos: Público y Privado</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
@@ -12418,17 +12410,17 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras</t>
+          <t>Auditoría de Proyectos: Público y Privado</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras y Servicios Relacionados</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras</t>
+          <t>Auditoría de Proyectos: Público y Privado</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
@@ -12446,22 +12438,22 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>), el estudiante que concluya las 43 asignaturas del presente plan, podrá optar por una de las siguientes seis modalidades</t>
+          <t>Auditoría de Entidades Financieras</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>) y con el Reglamento de Modalidades de Graduación de la Carrera incorporado en el punto 13.1.4, el estudiante que concluya las 43 asignaturas del presente plan podrá optar por una de las siguientes siete modalidades</t>
+          <t>Auditoría de Entidades Financieras y Servicios Relacionados</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>En estricta concordancia con el Reglamento General de Tipos y Modalidades de Graduación del SUB (aprobado en los congres</t>
+          <t>Auditoría de Entidades Financieras</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
@@ -12484,17 +12476,17 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>dedicación exclusiva durante un periodo máximo de 8 meses.</t>
+          <t>), el estudiante que concluya las 43 asignaturas del presente plan, podrá optar por una de las siguientes seis modalidades</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>dedicación exclusiva durante un periodo máximo de ocho (8) meses, con un mínimo de 1.280 horas de trabajo efectivo, conforme a los Artículos 46 y 47 del Reglamento de Modalidades de Graduación.</t>
+          <t>) y con el Reglamento de Modalidades de Graduación de la Carrera incorporado en el punto 13.1.4, el estudiante que concluya las 43 asignaturas del presente plan podrá optar por una de las siguientes siete modalidades</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Requisitos Específicos: El estudiante debe tener un promedio académico acumulado no menor a sesenta (60) puntos y dedica</t>
+          <t>En estricta concordancia con el Reglamento General de Tipos y Modalidades de Graduación del SUB (aprobado en los congres</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
@@ -12512,20 +12504,24 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Buena</t>
+          <t>dedicación exclusiva durante un periodo máximo de 8 meses.</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Bueno</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr"/>
+          <t>dedicación exclusiva durante un periodo máximo de ocho (8) meses, con un mínimo de 1.280 horas de trabajo efectivo, conforme a los Artículos 46 y 47 del Reglamento de Modalidades de Graduación.</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Requisitos Específicos: El estudiante debe tener un promedio académico acumulado no menor a sesenta (60) puntos y dedica</t>
+        </is>
+      </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12546,12 +12542,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Sobresaliente – Con recomendación de publicación</t>
+          <t>Aprobado – Buena</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Aprobado – Sobresaliente</t>
+          <t>Aprobado – Bueno</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr"/>
@@ -12575,12 +12571,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Excelente – Con mención honorífica y recomendación de publicación</t>
+          <t>Sobresaliente – Con recomendación de publicación</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Excelente – Excelencia</t>
+          <t>Aprobado – Sobresaliente</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr"/>
@@ -12599,24 +12595,20 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (escala del trabajo dirigido, Art. 55)</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>como mínimo tres (3) veces al año</t>
+          <t>Excelente – Con mención honorífica y recomendación de publicación</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>como mínimo cuatro (4) veces al año, cada convocatoria en tres (3) semanas continuas, una por ciclo</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
-        </is>
-      </c>
+          <t>Excelente – Excelencia</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12637,12 +12629,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>24 horas de anticipación al examen.</t>
+          <t>como mínimo tres (3) veces al año</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>24 horas de anticipación al examen. El postulante debe aprobar los tres ciclos en un plazo máximo de doce (12) meses calendario desde su inscripción al primer ciclo, y quien repruebe tres (3) veces un mismo ciclo queda inhabilitado para esta modalidad, conforme a los Artículos 60 a 67 del Reglamento de Modalidades de Graduación.</t>
+          <t>como mínimo cuatro (4) veces al año, cada convocatoria en tres (3) semanas continuas, una por ciclo</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -12670,17 +12662,17 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Ciclo Servicios</t>
+          <t>24 horas de anticipación al examen.</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Ciclo de Servicios</t>
+          <t>24 horas de anticipación al examen. El postulante debe aprobar los tres ciclos en un plazo máximo de doce (12) meses calendario desde su inscripción al primer ciclo, y quien repruebe tres (3) veces un mismo ciclo queda inhabilitado para esta modalidad, conforme a los Artículos 60 a 67 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Ciclo Servicios de Aseguramiento</t>
+          <t>Las asignaturas sujetas a evaluación, corresponden a las áreas de información financiera y aseguramiento, distribuidas e</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
@@ -12698,20 +12690,24 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Haber aprobado el 100% de las 43 asignaturas en primera instancia (sin haber recurrido a exámenes de mesa ni haber reprobado ninguna materia).</t>
+          <t>Ciclo Servicios</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Haber aprobado el 100% de las 43 asignaturas en evaluaciones ordinarias de primera instancia, sin haber reprobado, abandonado ni cursado asignaturas en segundo turno, exámenes extraordinarios de mesa o cursos de verano destinados a subsanar reprobaciones.</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr"/>
+          <t>Ciclo de Servicios</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Ciclo Servicios de Aseguramiento</t>
+        </is>
+      </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12732,12 +12728,12 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Haber concluido el plan de estudios dentro del tiempo reglamentario de la carrera (5 años continuos).</t>
+          <t>Haber aprobado el 100% de las 43 asignaturas en primera instancia (sin haber recurrido a exámenes de mesa ni haber reprobado ninguna materia).</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Haber concluido el plan de estudios en el tiempo reglamentario de cinco (5) gestiones académicas anuales continuas, sin suspensiones voluntarias, abandonos temporales ni postergaciones de matrícula.</t>
+          <t>Haber aprobado el 100% de las 43 asignaturas en evaluaciones ordinarias de primera instancia, sin haber reprobado, abandonado ni cursado asignaturas en segundo turno, exámenes extraordinarios de mesa o cursos de verano destinados a subsanar reprobaciones.</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr"/>
@@ -12761,12 +12757,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Acreditar un promedio general ponderado cuantitativo sobresaliente (igual o superior al límite fijado por la normativa de la Facultad y la UMSA).</t>
+          <t>Haber concluido el plan de estudios dentro del tiempo reglamentario de la carrera (5 años continuos).</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Acreditar un Promedio Ponderado Acumulado (PPA) igual o superior a setenta y cinco (75) puntos a lo largo de los cinco años de estudio, conforme al Artículo 72 del Reglamento de Modalidades de Graduación.</t>
+          <t>Haber concluido el plan de estudios en el tiempo reglamentario de cinco (5) gestiones académicas anuales continuas, sin suspensiones voluntarias, abandonos temporales ni postergaciones de matrícula.</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr"/>
@@ -12785,13 +12781,17 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72, requisito agregado)</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr"/>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72)</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Acreditar un promedio general ponderado cuantitativo sobresaliente (igual o superior al límite fijado por la normativa de la Facultad y la UMSA).</t>
+        </is>
+      </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>No registrar antecedentes disciplinarios, sanciones administrativas, procesos en Tribunal de Honor ni fallos de ética universitaria o de plagio académico.</t>
+          <t>Acreditar un Promedio Ponderado Acumulado (PPA) igual o superior a setenta y cinco (75) puntos a lo largo de los cinco años de estudio, conforme al Artículo 72 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr"/>
@@ -12810,24 +12810,16 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 78)</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>el estudiante de Quinto Año o egresado puede cursar</t>
-        </is>
-      </c>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 72, requisito agregado)</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr"/>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>el estudiante que concluyó y aprobó las 43 asignaturas del plan de estudios puede cursar</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
-        </is>
-      </c>
+          <t>No registrar antecedentes disciplinarios, sanciones administrativas, procesos en Tribunal de Honor ni fallos de ética universitaria o de plagio académico.</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr"/>
       <c r="F109" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12843,17 +12835,17 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación (Art. 78)</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa).</t>
+          <t>el estudiante de Quinto Año o egresado puede cursar</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa). Los programas duran entre cuatro (4) y seis (6) meses y exigen un 80 % de asistencia y una nota mínima de setenta y uno (71) puntos por módulo y en el trabajo final, conforme a los Artículos 77 a 82 del Reglamento de Modalidades de Graduación.</t>
+          <t>el estudiante que concluyó y aprobó las 43 asignaturas del plan de estudios puede cursar</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -12876,20 +12868,24 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Comentario eliminado</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Comentario de Carlos Gonzales Alanes: "Revisar los nombres de las asignaturas por favor"</t>
+          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa).</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Eliminado tras ajustar los nombres a la malla</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr"/>
+          <t>(otorgada al cursante con desempeño cuali-cuantitativo sobresaliente en los módulos del programa). Los programas duran entre cuatro (4) y seis (6) meses y exigen un 80 % de asistencia y una nota mínima de setenta y uno (71) puntos por módulo y en el trabajo final, conforme a los Artículos 77 a 82 del Reglamento de Modalidades de Graduación.</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Conforme a las normativas vigentes del SUB, mediante el Título IV (Artículos 82 al 95) del Reglamento General de Estudio</t>
+        </is>
+      </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12900,29 +12896,25 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>5.4.3</t>
+          <t>5.4.2</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Comentario eliminado</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Comentario de Carlos Gonzales Alanes: "Revisar los nombres de las asignaturas por favor"</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
-        </is>
-      </c>
+          <t>Eliminado tras ajustar los nombres a la malla</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr"/>
       <c r="F112" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -12938,17 +12930,17 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -12976,17 +12968,17 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior</t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior</t>
+          <t>Técnico Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>b. Técnico Universitario Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de</t>
+          <t>b. Técnico Universitario Superior. El grado de Técnico Universitario Superior en Contabilidad General se obtiene mediant</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
@@ -13004,20 +12996,24 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Descripción del grado intermedio TUM</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">a. Técnico Universitario Medio. Conforme al Artículo Segundo de la Resolución HCU N.º 426/2024, el requisito ineludible para extender el Diploma Académico y el Título Profesional de Técnico Universitario Medio es la aprobación de todas las asignaturas de primero y segundo año en el tiempo determinado de dos años, inexcusablemente. </t>
+          <t>Técnico Universitario Superior</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>a. Técnico Universitario Medio. Salida intermedia que conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr"/>
+          <t>Técnico Superior</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>b. Técnico Universitario Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de</t>
+        </is>
+      </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13033,24 +13029,20 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
+          <t>Descripción del grado intermedio TUM</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>se aprueba con nota mínima de 51 puntos sobre 100.</t>
+          <t xml:space="preserve">a. Técnico Universitario Medio. Conforme al Artículo Segundo de la Resolución HCU N.º 426/2024, el requisito ineludible para extender el Diploma Académico y el Título Profesional de Técnico Universitario Medio es la aprobación de todas las asignaturas de primero y segundo año en el tiempo determinado de dos años, inexcusablemente. </t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>se aprueba con nota mínima de 51 puntos sobre 100. La prueba es escrita, de resolución de casos sobre información financiera, con una duración de noventa (90) minutos, conforme a los Artículos 87 a 90 del Reglamento de Modalidades de Graduación.</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>b. Técnico Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de grado técnico</t>
-        </is>
-      </c>
+          <t>a. Técnico Universitario Medio. Salida intermedia que conduce a la obtención del Diploma Académico de Técnico Universitario Medio en Contabilidad y Título en Provisión Nacional de Auxiliar Contable, de aprobación directa tras concluir y aprobar la totalidad de las dieciséis (16) asignaturas correspondientes a primero y segundo año en un periodo continuo de dos (2) gestiones académicas, en estricto</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13061,27 +13053,27 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>6.2.2</t>
+          <t>5.4.3</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Alineación con el Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">digital,  </t>
+          <t>se aprueba con nota mínima de 51 puntos sobre 100.</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>digital,</t>
+          <t>se aprueba con nota mínima de 51 puntos sobre 100. La prueba es escrita, de resolución de casos sobre información financiera, con una duración de noventa (90) minutos, conforme a los Artículos 87 a 90 del Reglamento de Modalidades de Graduación.</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promover nuevos campos de investigación científica, especialmente aquellos que contribuyan a la construcción teórica de </t>
+          <t>b. Técnico Superior. El grado de Técnico Superior en Contabilidad General se obtiene mediante el examen de grado técnico</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
@@ -13094,25 +13086,29 @@
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.2.2</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Contenido duplicado eliminado</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>7.2Políticas y líneas de extensión universitaria | 7.2.1Políticas | Educación continua. La Carrera ofrece programas para diversos públicos interesados en las ares contables y financieras que son temas transversales para la gestión. | Articulación con el postgrado. La oferta de extensión se articula con la Unidad de Postgrado y con la modalidad de graduación mediante diplomado del punto 5.4.2. | Di</t>
+          <t xml:space="preserve">digital,  </t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Se conserva la segunda versión de 7.2 y 7.2.1, que contiene y amplía todos los ítems de la primera</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr"/>
+          <t>digital,</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promover nuevos campos de investigación científica, especialmente aquellos que contribuyan a la construcción teórica de </t>
+        </is>
+      </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13123,29 +13119,25 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Contenido duplicado eliminado</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>7.2Políticas y líneas de extensión universitaria | 7.2.1Políticas | Educación continua. La Carrera ofrece programas para diversos públicos interesados en las ares contables y financieras que son temas transversales para la gestión. | Articulación con el postgrado. La oferta de extensión se articula con la Unidad de Postgrado y con la modalidad de graduación mediante diplomado del punto 5.4.2. | Di</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>Se conserva la segunda versión de 7.2 y 7.2.1, que contiene y amplía todos los ítems de la primera</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr"/>
       <c r="F119" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13166,17 +13158,17 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr">
@@ -13199,17 +13191,17 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr">
@@ -13232,17 +13224,17 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Público y Privado</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Público y Privado</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr">
@@ -13265,17 +13257,17 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Público y Privado</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Público y Privado</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
@@ -13288,25 +13280,29 @@
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5. Estudiantes inscritos por asignatura y paralelo</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Estudiantes inscritos por asignatura y paralelo</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr"/>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13317,29 +13313,25 @@
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>9.1.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Cuadro 5. Estudiantes inscritos por asignatura y paralelo</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>Cuadro 6. Estudiantes inscritos por asignatura y paralelo</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13360,17 +13352,17 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr">
@@ -13393,17 +13385,17 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
@@ -13426,17 +13418,17 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
@@ -13459,17 +13451,17 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
@@ -13487,22 +13479,22 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Publica</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Contaduría Pública</t>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>La Carrera de Contaduría Publica actualmente cuenta con la siguiente bibliografía:</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
@@ -13515,25 +13507,29 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.1.2</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.143 estudiantes inscritos en 2025. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
+          <t>Contaduría Publica</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.116 estudiantes inscritos en 2026. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr"/>
+          <t>Contaduría Pública</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>La Carrera de Contaduría Publica actualmente cuenta con la siguiente bibliografía:</t>
+        </is>
+      </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13544,22 +13540,22 @@
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Requerimientos de recursos humanos</t>
+          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.143 estudiantes inscritos en 2025. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 9. Requerimientos de recursos humanos</t>
+          <t>Con 70 y 36 puestos, los laboratorios atienden simultáneamente a 106 estudiantes, frente a 3.116 estudiantes inscritos en 2026. Bajo el Rediseño Curricular, las asignaturas con componente tecnológico de cada año requerirán turnos de laboratorio en grupos reducidos, por lo que la capacidad de los lab</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr"/>
@@ -13573,22 +13569,22 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Resaltado de revisión eliminado</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 12. Ejecución presupuestaria de gastos, 2020 a 2026</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 10. Ejecución presupuestaria de gastos, 2020 a 2026</t>
+          <t>Sin resaltado</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr"/>
@@ -13602,22 +13598,22 @@
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 13. Fuentes de financiamiento complementario</t>
+          <t>Sin embargo, la plataforma Moodle tiene limitaciones en su capacidad en consideración de que existen 3184 estudiantes, ya que varios de los cuales se conectan simultáneamente.</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 11. Fuentes de financiamiento complementario</t>
+          <t>Sin embargo, la plataforma Moodle tiene limitaciones en su capacidad en consideración de que existen 3.116 estudiantes inscritos en la gestión 2026, varios de los cuales se conectan simultáneamente.</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr"/>
@@ -13641,12 +13637,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 14. Fases de implementación</t>
+          <t>Cuadro 11. Requerimientos de recursos humanos</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 12. Fases de implementación</t>
+          <t>Cuadro 9. Requerimientos de recursos humanos</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr"/>
@@ -13670,12 +13666,12 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 15. Riesgos de implementación y medidas de mitigación</t>
+          <t>Cuadro 12. Ejecución presupuestaria de gastos, 2020 a 2026</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 13. Riesgos de implementación y medidas de mitigación</t>
+          <t>Cuadro 10. Ejecución presupuestaria de gastos, 2020 a 2026</t>
         </is>
       </c>
       <c r="E136" s="7" t="inlineStr"/>
@@ -13689,18 +13685,22 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr"/>
+          <t>Numeración de cuadros</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Cuadro 13. Fuentes de financiamiento complementario</t>
+        </is>
+      </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
+          <t>Cuadro 11. Fuentes de financiamiento complementario</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr"/>
@@ -13714,22 +13714,22 @@
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entre 2021 y 2025, los estudiantes matriculados disminuyeron en 8,97 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+          <t>Cuadro 14. Fases de implementación</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+          <t>Cuadro 12. Fases de implementación</t>
         </is>
       </c>
       <c r="E138" s="7" t="inlineStr"/>
@@ -13743,22 +13743,22 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>11.1.1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+          <t>Cuadro 15. Riesgos de implementación y medidas de mitigación</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+          <t>Cuadro 13. Riesgos de implementación y medidas de mitigación</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr"/>
@@ -13780,14 +13780,10 @@
           <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
-        </is>
-      </c>
+      <c r="C140" s="7" t="inlineStr"/>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.180, todavía representa </t>
+          <t>Columna 2026 agregada: 2026 | 4.296 | 3.116 | 1.180</t>
         </is>
       </c>
       <c r="E140" s="7" t="inlineStr"/>
@@ -13801,7 +13797,7 @@
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>11.1.3</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -13811,12 +13807,12 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>4.283 matriculados y 3.143 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
+          <t xml:space="preserve">Entre 2021 y 2025, los estudiantes matriculados disminuyeron en 8,97 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>4.296 matriculados y 3.116 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr"/>
@@ -13830,29 +13826,25 @@
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>especifico de un aula</t>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.143. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>específico de un aula</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>Equipamiento especifico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13863,29 +13855,25 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>11.1.1</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>clases hibridas</t>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.140, todavía representa </t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>clases híbridas</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>Equipamiento específico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Entre 2021 y 2026, los estudiantes matriculados disminuyeron en 8,69 %, mientras que los inscritos se mantuvieron estables, con una variación de 3.152 a 3.116. La diferencia corresponde a estudiantes que se matriculan pero no cursan asignaturas; aunque se redujo de 1.553 a 1.180, todavía representa </t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13896,29 +13884,25 @@
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>11.1.4</t>
+          <t>11.1.3</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>auditoria</t>
+          <t>4.283 matriculados y 3.143 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>auditoría</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>Dotación de software de acuerdo a las necesidades del itinerario formativo, por ejemplo: Software de auditoria, Gestores</t>
-        </is>
-      </c>
+          <t>4.296 matriculados y 3.116 inscritos; 974 plazas en las aulas del Edificio Nava Morales; biblioteca con 90 plazas</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13939,17 +13923,17 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliografico</t>
+          <t>especifico de un aula</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliográfico</t>
+          <t>específico de un aula</t>
         </is>
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>Material Bibliografico</t>
+          <t>Equipamiento especifico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
@@ -13962,25 +13946,29 @@
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>11.2.1</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contable y de Auditoría</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas troncales. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servidores, 10 de planta y 13</t>
+          <t>clases hibridas</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas del Área Contable y de Auditoría. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servid</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr"/>
+          <t>clases híbridas</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>Equipamiento específico de un aula para clases hibridas que permitan la conexión con estudiantes y/o docentes de forma r</t>
+        </is>
+      </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -13991,25 +13979,29 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>11.2.1</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Término: Contador Público</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
+          <t>auditoria</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr"/>
+          <t>auditoría</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>Dotación de software de acuerdo a las necesidades del itinerario formativo, por ejemplo: Software de auditoria, Gestores</t>
+        </is>
+      </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14020,27 +14012,27 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>11.1.4</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>Herramientas Digitales</t>
+          <t>Material Bibliografico</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Tecnologías de Información y Herramientas Digitales</t>
+          <t>Material Bibliográfico</t>
         </is>
       </c>
       <c r="E148" s="7" t="inlineStr">
         <is>
-          <t>CPA-102 Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contaduría Pública / Auditoría con Tí</t>
+          <t>Material Bibliografico</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
@@ -14053,29 +14045,25 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>11.2.1</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>Sistemas ERP y Analítica</t>
+          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas troncales. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servidores, 10 de planta y 13</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Sistemas Contables ERP y Análisis de Datos</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>CPA-102 Tecnologías de Información y Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contadur</t>
-        </is>
-      </c>
+          <t>Como apoyo a la docencia, la Carrera cuenta con 79 ítems de auxiliares de docencia, que priorizan las asignaturas del Área Contable y de Auditoría. El Instituto de Investigaciones dispone de 320 horas mensuales y su Dirección se encuentra acéfala desde 2022. El personal administrativo suma 23 servid</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14086,29 +14074,25 @@
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>11.2.2</t>
+          <t>11.2.1</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>Métodos de Investigación</t>
+          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Métodos y Técnicas de Investigación</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>CPA-204 Métodos de Investigación: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional de Con</t>
-        </is>
-      </c>
+          <t>Los datos muestran tres debilidades. Primero, más de la mitad de las designaciones corresponde a docentes interinos e invitados, lo que afecta la estabilidad pedagógica y la continuidad de la investigación y la interacción social. Segundo, el área de Servicios de Aseguramiento, núcleo profesional de</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14129,17 +14113,17 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Digital y Ciberseguridad</t>
+          <t>Herramientas Digitales</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Digital, Ciberseguridad y Tecnologías Emergentes</t>
+          <t>Tecnologías de Información y Herramientas Digitales</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>CPA-505 Auditoría Digital y Ciberseguridad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacio</t>
+          <t>CPA-102 Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contaduría Pública / Auditoría con Tí</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
@@ -14162,17 +14146,17 @@
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>Reportes y Aseguramiento de Sostenibilidad</t>
+          <t>Sistemas ERP y Analítica</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Reportes y Aseguramiento de Sostenibilidad y Auditoría Ambiental</t>
+          <t>Sistemas Contables ERP y Análisis de Datos</t>
         </is>
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>CPA-506 Reportes y Aseguramiento de Sostenibilidad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisi</t>
+          <t>CPA-102 Tecnologías de Información y Herramientas Digitales y CPA-305 Sistemas ERP y Analítica: Licenciatura en Contadur</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
@@ -14195,17 +14179,17 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Peritajes</t>
+          <t>Métodos de Investigación</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+          <t>Métodos y Técnicas de Investigación</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>CPA-508 Auditoría Forense y Peritajes: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional d</t>
+          <t>CPA-204 Métodos de Investigación: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional de Con</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
@@ -14223,22 +14207,22 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>Contador Publico</t>
+          <t>Auditoría Digital y Ciberseguridad</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Contador Público</t>
+          <t>Auditoría Digital, Ciberseguridad y Tecnologías Emergentes</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+          <t>CPA-505 Auditoría Digital y Ciberseguridad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacio</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
@@ -14256,22 +14240,22 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Reportes y Aseguramiento de Sostenibilidad</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Reportes y Aseguramiento de Sostenibilidad y Auditoría Ambiental</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+          <t>CPA-506 Reportes y Aseguramiento de Sostenibilidad: Licenciatura en Contaduría Pública / Auditoría con Título en Provisi</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
@@ -14289,20 +14273,24 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular 2027 y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen los siguientes perfi</t>
+          <t>Auditoría Forense y Peritajes</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular del Rediseño Curricular y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen l</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr"/>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>CPA-508 Auditoría Forense y Peritajes: Licenciatura en Contaduría Pública / Auditoría con Título en Provisión Nacional d</t>
+        </is>
+      </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14313,25 +14301,29 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>11.3.1</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>Para evaluar la capacidad financiera que respaldará la implementación del Plan 2027, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
+          <t>Contador Publico</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Para evaluar la capacidad financiera que respaldará la implementación del Rediseño Curricular, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="inlineStr"/>
+          <t>Contador Público</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+        </is>
+      </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14342,25 +14334,29 @@
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>11.3.2</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Plan 2027 se rige por los siguiente</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Rediseño Curricular se rige por los</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr"/>
+          <t>Auditoría</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>Licenciatura en Derecho con Título en Provisión Nacional de Abogado o Licenciatura en Contaduría Pública / Auditoria con</t>
+        </is>
+      </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14371,29 +14367,25 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.2.2</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular 2027 y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen los siguientes perfi</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>12.1.2</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>12.1.3Componentes de la evaluación</t>
-        </is>
-      </c>
+          <t>Dada la naturaleza especializada de las seis áreas del conocimiento que conforman la malla curricular del Rediseño Curricular y en cumplimiento de las Normas IES 2 e IES 4 de la IFAC, del Reglamento de Acreditación de la UMSA (Resolución HCU Nº 443/2025) y de los estándares del CEUB, se establecen l</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14404,29 +14396,25 @@
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.3.1</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>Para evaluar la capacidad financiera que respaldará la implementación del Plan 2027, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>12.1.3</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>12.1.5Dimensiones de la evaluación del plan de estudios</t>
-        </is>
-      </c>
+          <t>Para evaluar la capacidad financiera que respaldará la implementación del Rediseño Curricular, se analizó la ejecución presupuestaria de gastos de la Carrera desde 2020:</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14437,29 +14425,25 @@
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.3.2</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>Numeración de subpuntos</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Plan 2027 se rige por los siguiente</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>12.1.4</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>12.1.6Seguimiento del desarrollo curricular</t>
-        </is>
-      </c>
+          <t>La modernización curricular requiere recursos recurrentes para software especializado, actualización de laboratorios y ampliación de la carga horaria docente, que no pueden sostenerse con un presupuesto inercial y una ejecución baja. La política presupuestaria del Rediseño Curricular se rige por los</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14480,17 +14464,17 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>12.1.7</t>
+          <t>12.1.3</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>12.1.5</t>
+          <t>12.1.2</t>
         </is>
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>12.1.7Mecanismos de seguimiento anual</t>
+          <t>12.1.3Componentes de la evaluación</t>
         </is>
       </c>
       <c r="F162" s="9" t="inlineStr">
@@ -14513,17 +14497,17 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>12.1.9</t>
+          <t>12.1.5</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>12.1.6</t>
+          <t>12.1.3</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>12.1.9Evaluación del plan al concluir su implementación</t>
+          <t>12.1.5Dimensiones de la evaluación del plan de estudios</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
@@ -14546,17 +14530,17 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>12.1.10</t>
+          <t>12.1.6</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>12.1.7</t>
+          <t>12.1.4</t>
         </is>
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>12.1.10Responsables y uso de los resultados</t>
+          <t>12.1.6Seguimiento del desarrollo curricular</t>
         </is>
       </c>
       <c r="F164" s="9" t="inlineStr">
@@ -14569,27 +14553,27 @@
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>12.1.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Ortografía</t>
+          <t>Numeración de subpuntos</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>estudiantes  por</t>
+          <t>12.1.7</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>estudiantes por</t>
+          <t>12.1.5</t>
         </is>
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>Tasa de egreso en los cinco años previstos y con uno o dos años de rezago; tasa de titulación por cohorte; retención y a</t>
+          <t>12.1.7Mecanismos de seguimiento anual</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
@@ -14602,25 +14586,29 @@
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Numeración de subpuntos</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>Este punto identifica la normativa universitaria que rige el Plan de Estudios 2027, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del I</t>
+          <t>12.1.9</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>Este punto identifica la normativa universitaria que rige el Rediseño Curricular, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del Ins</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr"/>
+          <t>12.1.6</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>12.1.9Evaluación del plan al concluir su implementación</t>
+        </is>
+      </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14631,25 +14619,29 @@
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t>13.1.1</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Numeración de subpuntos</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1. Normativa universitaria aplicable al Plan 2027</t>
+          <t>12.1.10</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1. Normativa universitaria aplicable al Rediseño Curricular</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr"/>
+          <t>12.1.7</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>12.1.10Responsables y uso de los resultados</t>
+        </is>
+      </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14660,27 +14652,27 @@
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>13.1.2</t>
+          <t>12.1.3</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>Referencia cruzada</t>
+          <t>Ortografía</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>Puntos 4.7.5 y 5.3</t>
+          <t>estudiantes  por</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Puntos 5.3.3 y 5.3.4</t>
+          <t>estudiantes por</t>
         </is>
       </c>
       <c r="E168" s="7" t="inlineStr">
         <is>
-          <t>Puntos 4.7.5 y 5.3</t>
+          <t>Tasa de egreso en los cinco años previstos y con uno o dos años de rezago; tasa de titulación por cohorte; retención y a</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
@@ -14693,7 +14685,7 @@
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t>13.1.2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -14703,12 +14695,12 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>La implementación del Plan 2027 requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a partir de la Re</t>
+          <t>Este punto identifica la normativa universitaria que rige el Plan de Estudios 2027, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del I</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>La implementación del Rediseño Curricular requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a parti</t>
+          <t>Este punto identifica la normativa universitaria que rige el Rediseño Curricular, establece los reglamentos internos que la Carrera debe mantener, actualizar o elaborar para su implementación, y presenta el Reglamento de Modalidades de Graduación actualizado al nuevo plan y la reglamentación del Ins</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
@@ -14722,7 +14714,7 @@
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t>13.1.2</t>
+          <t>13.1.1</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -14732,12 +14724,12 @@
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 2. Reglamentos internos para la implementación del Plan 2027</t>
+          <t>Cuadro 1. Normativa universitaria aplicable al Plan 2027</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 2. Reglamentos internos para la implementación del Rediseño Curricular</t>
+          <t>Cuadro 1. Normativa universitaria aplicable al Rediseño Curricular</t>
         </is>
       </c>
       <c r="E170" s="7" t="inlineStr"/>
@@ -14751,29 +14743,25 @@
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>13.1.1</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Referencia cruzada</t>
+          <t>Resaltado de revisión eliminado</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>conforme al punto 4.7.5.</t>
+          <t>Resolución HCU N.º 538/2022</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>conforme al punto 5.3.4.</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las mesas de examen se rigen por la Resolución HCU N.º 352/2021, cuyo Artículo 8 las limita a las materias teóricas del </t>
-        </is>
-      </c>
+          <t>Sin resaltado</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14784,22 +14772,22 @@
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>13.1.1</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Resaltado de revisión eliminado</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+          <t>Campus Virtual UMSA-Coursera</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+          <t>Sin resaltado</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr"/>
@@ -14813,25 +14801,29 @@
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t>13.1.3</t>
+          <t>13.1.2</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contable y de Auditoría y Área Contextual</t>
+          <t>Referencia cruzada</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
+          <t>Puntos 4.7.5 y 5.3</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr"/>
+          <t>Puntos 5.3.3 y 5.3.4</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>Puntos 4.7.5 y 5.3</t>
+        </is>
+      </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14842,7 +14834,7 @@
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>13.1.2</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
@@ -14852,12 +14844,12 @@
       </c>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
+          <t>La implementación del Plan 2027 requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a partir de la Re</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
+          <t>La implementación del Rediseño Curricular requiere actualizar los reglamentos internos vigentes y elaborar los que exigen las innovaciones del plan. Los reglamentos internos vigentes forman parte del Manual de Funciones y Reglamentos de la Carrera, aprobado por la Resolución HCU N.º 139/2013 a parti</t>
         </is>
       </c>
       <c r="E174" s="7" t="inlineStr"/>
@@ -14871,7 +14863,7 @@
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>13.1.2</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
@@ -14881,12 +14873,12 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>De conformidad con el Plan de Estudios 2027 y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
+          <t>Cuadro 2. Reglamentos internos para la implementación del Plan 2027</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>De conformidad con el Rediseño Curricular y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
+          <t>Cuadro 2. Reglamentos internos para la implementación del Rediseño Curricular</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr"/>
@@ -14900,25 +14892,29 @@
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>13.1.3</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Referencia cruzada</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Plan de Estudios 2027, se reconocen oficialmente las siguientes modalidades:</t>
+          <t>conforme al punto 4.7.5.</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Rediseño Curricular, se reconocen oficialmente las siguientes modalidades:</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr"/>
+          <t>conforme al punto 5.3.4.</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las mesas de examen se rigen por la Resolución HCU N.º 352/2021, cuyo Artículo 8 las limita a las materias teóricas del </t>
+        </is>
+      </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -14929,7 +14925,7 @@
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>13.1.3</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -14939,12 +14935,12 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr"/>
@@ -14958,22 +14954,22 @@
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
         <is>
-          <t>13.1.4</t>
+          <t>13.1.3</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Término: Área Contable y de Auditoría</t>
+          <t>Término: Área Contable y de Auditoría y Área Contextual</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas troncales del ciclo intermedio (Primer a Tercer año).</t>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas del Área Contable y de Auditoría del ciclo intermedio (Primer a Tercer año).</t>
+          <t>Los cursos de temporada se rigen por la Resolución HCU N.º 093/2006, cuyo Artículo 13 otorga a las carreras la tuición de elegir las asignaturas que se dictan, con la obligación de cubrir el 100 % de sus contenidos en teoría y en práctica, y cuyo Artículo 6 fija una duración mínima de 60 días calend</t>
         </is>
       </c>
       <c r="E178" s="7" t="inlineStr"/>
@@ -14992,17 +14988,17 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Término: Contador Público</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
+          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
+          <t>El presente Reglamento Específico de Modalidades de Graduación de la Carrera de Contaduría Pública entrará en vigencia plena a partir del día siguiente de su homologación y promulgación mediante Resolución del Honorable Consejo Facultativo de Ciencias Económicas y Financieras y del Honorable Consejo</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr"/>
@@ -15021,24 +15017,20 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>Él o los Docentes</t>
+          <t>De conformidad con el Plan de Estudios 2027 y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>El o los Docentes</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>4 vez/veces</t>
-        </is>
-      </c>
+          <t>De conformidad con el Rediseño Curricular y la estructura de titulación de la Carrera de Contaduría Pública, se otorgan y tramitan tres (3) niveles de titulación universitaria:</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15054,24 +15046,20 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>la División, de Gestiones</t>
+          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Plan de Estudios 2027, se reconocen oficialmente las siguientes modalidades:</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>la División de Gestiones</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>En estricto apego al catálogo del Sistema de la Universidad Boliviana y al Rediseño Curricular, se reconocen oficialmente las siguientes modalidades:</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr"/>
       <c r="F181" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15087,24 +15075,20 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencia Económicas</t>
+          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Los estudiantes inscritos en planes de estudio anteriores (Plan 2013 o precedentes) que concluyan sus asignaturas durante el periodo de transición curricular mantendrán el derecho a graduarse bajo las modalidades vigentes al momento de su conclusión de estudios, o podrán acogerse voluntariamente a l</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr"/>
       <c r="F182" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15120,24 +15104,20 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Término: Área Contable y de Auditoría</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>expedido la Unidad</t>
+          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas troncales del ciclo intermedio (Primer a Tercer año).</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>expedido por la Unidad</t>
-        </is>
-      </c>
-      <c r="E183" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>Examen de Grado Técnico Superior: Evaluación comprensiva sobre las ocho (8) asignaturas del Área Contable y de Auditoría del ciclo intermedio (Primer a Tercer año).</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr"/>
       <c r="F183" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15153,24 +15133,20 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
+          <t>Término: Contador Público</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>En caso, de no existir</t>
+          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>En caso de no existir</t>
-        </is>
-      </c>
-      <c r="E184" s="7" t="inlineStr">
-        <is>
-          <t>1 vez/veces</t>
-        </is>
-      </c>
+          <t>El Trabajo Dirigido es una modalidad de graduación que consiste en la ejecución de un trabajo práctico preprofesional, supervisado, fiscalizado y evaluado, desarrollado en instituciones públicas, empresas privadas o dependencias de la Universidad Mayor de San Andrés (UMSA). Su finalidad es aplicar l</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr"/>
       <c r="F184" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15191,17 +15167,17 @@
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>veintiún 21)</t>
+          <t>Él o los Docentes</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>veintiún (21)</t>
+          <t>El o los Docentes</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>1 vez/veces</t>
+          <t>4 vez/veces</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
@@ -15224,12 +15200,12 @@
       </c>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Kardex Académico:  Expedido</t>
+          <t>la División, de Gestiones</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Kardex Académico: Expedido</t>
+          <t>la División de Gestiones</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
@@ -15257,12 +15233,12 @@
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas, a lo largo</t>
+          <t>Facultad de Ciencia Económicas</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Facultad de Ciencias Económicas), a lo largo</t>
+          <t>Facultad de Ciencias Económicas</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
@@ -15290,12 +15266,12 @@
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior – Contador General</t>
+          <t>expedido la Unidad</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior – Contador General)</t>
+          <t>expedido por la Unidad</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
@@ -15318,17 +15294,17 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>Auxiliar en Contabilidad General</t>
+          <t>En caso, de no existir</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Auxiliar Contable</t>
+          <t>En caso de no existir</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
@@ -15351,17 +15327,17 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>Presupuestos y Contabilidad Gubernamental (CPA-304)</t>
+          <t>veintiún 21)</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental (CPA-304)</t>
+          <t>veintiún (21)</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
@@ -15384,17 +15360,17 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Kardex Académico:  Expedido</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
+          <t>Kardex Académico: Expedido</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
@@ -15417,17 +15393,17 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos (CPA-408)</t>
+          <t>Facultad de Ciencias Económicas, a lo largo</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo (CPA-408)</t>
+          <t>Facultad de Ciencias Económicas), a lo largo</t>
         </is>
       </c>
       <c r="E192" s="7" t="inlineStr">
@@ -15450,17 +15426,17 @@
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
+          <t>Reglamento de Modalidades de Graduación: ortografía o puntuación</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos: Público y Privado (CPA-507)</t>
+          <t>Técnico Superior – Contador General</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos (CPA-507)</t>
+          <t>Técnico Superior – Contador General)</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
@@ -15488,12 +15464,12 @@
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras (CPA-509)</t>
+          <t>Auxiliar en Contabilidad General</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Financieras y Servicios Relacionados (CPA-509)</t>
+          <t>Auxiliar Contable</t>
         </is>
       </c>
       <c r="E194" s="7" t="inlineStr">
@@ -15516,20 +15492,24 @@
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación</t>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Texto anterior del punto 13.1.4 (83 párrafos y tablas: 46 artículos en 6 capítulos)</t>
+          <t>Presupuestos y Contabilidad Gubernamental (CPA-304)</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Reemplazado por el Reglamento de Modalidades de Graduación íntegro (Capítulos I a X, Artículos 1 a 90 y 87-Bis, Disposiciones Transitorias y Finales), con el formato del documento</t>
-        </is>
-      </c>
-      <c r="E195" s="7" t="inlineStr"/>
+          <t>Presupuesto y Contabilidad Gubernamental (CPA-304)</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15545,20 +15525,24 @@
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>Reglamento de Modalidades de Graduación</t>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
         <is>
-          <t>Párrafos partidos en el original (Art. 47 «, estando obligado…» y ponderación del Art. 55 en cinco líneas)</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Unidos en un solo párrafo cada uno</t>
-        </is>
-      </c>
-      <c r="E196" s="7" t="inlineStr"/>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15569,25 +15553,29 @@
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
         <is>
-          <t>13.2.2</t>
+          <t>13.1.4</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>Numeración de cuadros</t>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos (CPA-408)</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
-        </is>
-      </c>
-      <c r="E197" s="7" t="inlineStr"/>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo (CPA-408)</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15598,25 +15586,29 @@
     <row r="198">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>13.2.2</t>
+          <t>13.1.4</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>El reglamento interno del Instituto se actualizará para articularlo con el Plan 2027 con base en los siguientes lineamientos:</t>
+          <t>Auditoría de Proyectos: Público y Privado (CPA-507)</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>El reglamento interno del Instituto se actualizará para articularlo con el Rediseño Curricular con base en los siguientes lineamientos:</t>
-        </is>
-      </c>
-      <c r="E198" s="7" t="inlineStr"/>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos (CPA-507)</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15627,25 +15619,29 @@
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>13.1.4</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Reglamento de Modalidades de Graduación: nombre de asignatura o grado</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.143 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
+          <t>Auditoría de Entidades Financieras (CPA-509)</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.116 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
-        </is>
-      </c>
-      <c r="E199" s="7" t="inlineStr"/>
+          <t>Auditoría de Entidades Financieras y Servicios Relacionados (CPA-509)</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>1 vez/veces</t>
+        </is>
+      </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15656,22 +15652,22 @@
     <row r="200">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>14.9.1</t>
+          <t>13.1.4</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
         <is>
-          <t>Datos de matrícula, gestión 2026</t>
+          <t>Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>Frente a 4.283 estudiantes matriculados y 3.143 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
+          <t>Texto anterior del punto 13.1.4 (83 párrafos y tablas: 46 artículos en 6 capítulos)</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Frente a 4.296 estudiantes matriculados y 3.116 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
+          <t>Reemplazado por el Reglamento de Modalidades de Graduación íntegro (Capítulos I a X, Artículos 1 a 90 y 87-Bis, Disposiciones Transitorias y Finales), con el formato del documento</t>
         </is>
       </c>
       <c r="E200" s="7" t="inlineStr"/>
@@ -15685,22 +15681,22 @@
     <row r="201">
       <c r="A201" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13.1.4</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Reglamento de Modalidades de Graduación</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Plan de Estudios 2027: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementac</t>
+          <t>Párrafos partidos en el original (Art. 47 «, estando obligado…» y ponderación del Art. 55 en cinco líneas)</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Rediseño Curricular: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementació</t>
+          <t>Unidos en un solo párrafo cada uno</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr"/>
@@ -15714,22 +15710,22 @@
     <row r="202">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>16.1.1</t>
+          <t>13.2.2</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Numeración de cuadros</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Plan 2027 mediante homologación o convalidación.</t>
+          <t>Cuadro 6. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Rediseño Curricular mediante homologación o convalidación.</t>
+          <t>Cuadro 3. Lineamientos del reglamento interno del Instituto de Investigaciones</t>
         </is>
       </c>
       <c r="E202" s="7" t="inlineStr"/>
@@ -15743,7 +15739,7 @@
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
         <is>
-          <t>16.1.1</t>
+          <t>13.2.2</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -15753,12 +15749,12 @@
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Plan 2027.</t>
+          <t>El reglamento interno del Instituto se actualizará para articularlo con el Plan 2027 con base en los siguientes lineamientos:</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Rediseño Curricular.</t>
+          <t>El reglamento interno del Instituto se actualizará para articularlo con el Rediseño Curricular con base en los siguientes lineamientos:</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr"/>
@@ -15772,22 +15768,22 @@
     <row r="204">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>16.1.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>Implantación gradual. El Plan 2027 se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
+          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.143 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>Implantación gradual. El Rediseño Curricular se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
+          <t>La sala de lectura ofrece 0,57 m² por usuario a plena capacidad y 90 plazas para 3.116 estudiantes inscritos. Cuenta con dos cámaras de seguridad y aire acondicionado. El acervo de 6.173 libros y 2.821 trabajos académicos, el sistema KOHA, el repositorio institucional y el acceso a bases de datos se</t>
         </is>
       </c>
       <c r="E204" s="7" t="inlineStr"/>
@@ -15801,29 +15797,25 @@
     <row r="205">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>14.9.1</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Datos de matrícula, gestión 2026</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+          <t>Frente a 4.283 estudiantes matriculados y 3.143 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Álgebra Lineal y Modelación para Negocios</t>
-        </is>
-      </c>
-      <c r="E205" s="7" t="inlineStr">
-        <is>
-          <t>MAT-201 Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
-        </is>
-      </c>
+          <t>Frente a 4.296 estudiantes matriculados y 3.116 inscritos, la infraestructura de la Carrera es insuficiente: las aulas de los primeros años están saturadas, los laboratorios atienden simultáneamente a 106 estudiantes, la sala de lectura ofrece 90 plazas y la sala de docentes, 18. La dispersión entre</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr"/>
       <c r="F205" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15834,29 +15826,25 @@
     <row r="206">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C206" s="7" t="inlineStr">
         <is>
-          <t>Contabilidad y Presupuestos Gubernamental</t>
+          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Plan de Estudios 2027: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementac</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>Presupuesto y Contabilidad Gubernamental</t>
-        </is>
-      </c>
-      <c r="E206" s="7" t="inlineStr">
-        <is>
-          <t>CPA-304 Contabilidad y Presupuestos Gubernamental</t>
-        </is>
-      </c>
+          <t>Este punto establece las reglas para el tránsito del Plan de Estudios 2013, aprobado mediante las Resoluciones HCC N.º 162/2012, HCF N.º 929/2012 y HCU N.º 025/2013, al Rediseño Curricular: el cuadro de convalidación y homologación de asignaturas para estudiantes y docentes, el plan de implementació</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr"/>
       <c r="F206" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15867,29 +15855,25 @@
     <row r="207">
       <c r="A207" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>16.1.1</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Plan 2027 mediante homologación o convalidación.</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="inlineStr">
-        <is>
-          <t>CPA-408 Auditoría Interna, Control Interno y Gestión de Riesgos</t>
-        </is>
-      </c>
+          <t>Respeto a los derechos adquiridos de los estudiantes. Toda asignatura aprobada en el Plan 2013 conserva su validez y se reconoce en el Rediseño Curricular mediante homologación o convalidación.</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr"/>
       <c r="F207" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15900,29 +15884,25 @@
     <row r="208">
       <c r="A208" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>16.1.1</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Proyectos Públicos y Privados</t>
+          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Plan 2027.</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>CPA-507 Auditoría de Proyectos Públicos y Privados</t>
-        </is>
-      </c>
+          <t>Respeto a los derechos adquiridos de los docentes. Se garantiza la titularidad obtenida por concurso de méritos y examen de competencia en el Plan 2013, con la asignación de la cátedra equivalente en el Rediseño Curricular.</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr"/>
       <c r="F208" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15933,29 +15913,25 @@
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>16.1.3</t>
+          <t>16.1.1</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
         <is>
-          <t>Nombre de asignatura (malla definitiva)</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+          <t>Implantación gradual. El Plan 2027 se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
-      <c r="E209" s="7" t="inlineStr">
-        <is>
-          <t>CPA-508 Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
-        </is>
-      </c>
+          <t>Implantación gradual. El Rediseño Curricular se aplica año por año desde 2027, y el Plan 2013 se extingue de forma progresiva conforme al punto 16.3.</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr"/>
       <c r="F209" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -15971,20 +15947,24 @@
       </c>
       <c r="B210" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
+          <t>Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
-        </is>
-      </c>
-      <c r="E210" s="7" t="inlineStr"/>
+          <t>Álgebra Lineal y Modelación para Negocios</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>MAT-201 Álgebra Lineal y Programación Operativa Aplicada a los Negocios</t>
+        </is>
+      </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16000,20 +15980,24 @@
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Plan 2027:</t>
+          <t>Contabilidad y Presupuestos Gubernamental</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Rediseño Curricular:</t>
-        </is>
-      </c>
-      <c r="E211" s="7" t="inlineStr"/>
+          <t>Presupuesto y Contabilidad Gubernamental</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>CPA-304 Contabilidad y Presupuestos Gubernamental</t>
+        </is>
+      </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16029,20 +16013,24 @@
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Plan de Estudios 2027</t>
+          <t>Auditoría Interna, Control Interno y Gestión de Riesgos</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Rediseño Curricular</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="inlineStr"/>
+          <t>Auditoría Interna, Control Interno, Gestión de Riesgos y Gobierno Corporativo</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>CPA-408 Auditoría Interna, Control Interno y Gestión de Riesgos</t>
+        </is>
+      </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16058,20 +16046,24 @@
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>Asignatura equivalente del Plan 2027</t>
+          <t>Auditoría de Proyectos Públicos y Privados</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Asignatura equivalente del Rediseño Curricular</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="inlineStr"/>
+          <t>Auditoría de Entidades Sin Fines de Lucro – Proyectos Privados y Públicos</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>CPA-507 Auditoría de Proyectos Públicos y Privados</t>
+        </is>
+      </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16087,20 +16079,24 @@
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Nombre de asignatura (malla definitiva)</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Plan 2027.</t>
+          <t>Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Rediseño Curricular.</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="inlineStr"/>
+          <t>Auditoría Forense y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>CPA-508 Auditoría Forense, Peritaje y Prevención de Delitos Económicos</t>
+        </is>
+      </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16126,7 +16122,7 @@
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Rediseño Curricular</t>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr"/>
@@ -16150,12 +16146,12 @@
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>Fuente: elaboración con base en la malla curricular 2027 y en la propuesta de equivalencias de la Carrera.</t>
+          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Plan 2027:</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>Fuente: elaboración con base en la malla curricular del Rediseño Curricular y en la propuesta de equivalencias de la Carrera.</t>
+          <t>El siguiente cuadro rige para los estudiantes, que obtienen el reconocimiento de las asignaturas aprobadas, y para los docentes titulares, que obtienen la homologación de su cátedra en la asignatura equivalente. Las 43 asignaturas del Plan 2013 tienen equivalente en el Rediseño Curricular:</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr"/>
@@ -16169,7 +16165,7 @@
     <row r="217">
       <c r="A217" s="8" t="inlineStr">
         <is>
-          <t>16.1.4</t>
+          <t>16.1.3</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
@@ -16179,12 +16175,12 @@
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Plan 2027 en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
+          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Plan de Estudios 2027</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Rediseño Curricular en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
+          <t>Cuadro 1. Equivalencias entre el Plan de Estudios 2013 y el Rediseño Curricular</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr"/>
@@ -16198,7 +16194,7 @@
     <row r="218">
       <c r="A218" s="8" t="inlineStr">
         <is>
-          <t>16.1.4</t>
+          <t>16.1.3</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
@@ -16208,12 +16204,12 @@
       </c>
       <c r="C218" s="7" t="inlineStr">
         <is>
-          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Plan 2027 que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
+          <t>Asignatura equivalente del Plan 2027</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Rediseño Curricular que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
+          <t>Asignatura equivalente del Rediseño Curricular</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr"/>
@@ -16227,7 +16223,7 @@
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
         <is>
-          <t>16.1.4</t>
+          <t>16.1.3</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
@@ -16237,12 +16233,12 @@
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Plan 2027. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de actualizació</t>
+          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Plan 2027.</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Rediseño Curricular. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de ac</t>
+          <t>De las 43 asignaturas, 34 se homologan directamente, 4 se homologan con cambio de nivel o actualización de contenidos y 5 se convalidan por la actualización tecnológica o normativa de sus contenidos: CPA-102, CPA-305, CPA-505, CPA-506 y MAT-201 del Rediseño Curricular.</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr"/>
@@ -16256,29 +16252,25 @@
     <row r="220">
       <c r="A220" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1.3</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
         <is>
-          <t>Técnico Universitario Superior en Contabilidad General</t>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Plan 2027</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>Técnico Superior en Contabilidad General</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Habilitación de la salida intermedia de Técnico Universitario Superior en Contabilidad General; planes de asignatura de </t>
-        </is>
-      </c>
+          <t>16.1.3Cuadro de equivalencias entre el Plan 2013 y el Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr"/>
       <c r="F220" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16289,29 +16281,25 @@
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1.3</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>Referencia cruzada</t>
+          <t>Término: Rediseño Curricular</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>12.1.5.</t>
+          <t>Fuente: elaboración con base en la malla curricular 2027 y en la propuesta de equivalencias de la Carrera.</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>12.1.3.</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>Fuente: elaboración con base en los puntos 11.3.4 y 12.1.5.</t>
-        </is>
-      </c>
+          <t>Fuente: elaboración con base en la malla curricular del Rediseño Curricular y en la propuesta de equivalencias de la Carrera.</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr"/>
       <c r="F221" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16322,7 +16310,7 @@
     <row r="222">
       <c r="A222" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1.4</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -16332,12 +16320,12 @@
       </c>
       <c r="C222" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 2. Cronograma de implementación del Plan 2027</t>
+          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Plan 2027 en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 2. Cronograma de implementación del Rediseño Curricular</t>
+          <t>El estudiante del Plan 2013 puede migrar voluntariamente al Rediseño Curricular en cualquier momento de la transición, con el reconocimiento de todas sus asignaturas aprobadas según el Cuadro 1. La migración es irreversible.</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr"/>
@@ -16351,7 +16339,7 @@
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1.4</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -16361,12 +16349,12 @@
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>Plan de Estudios 2027</t>
+          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Plan 2027 que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Rediseño Curricular</t>
+          <t>Las asignaturas que cambian de año, como CPA-102, CPA-204, CPA-305, CPA-406 y MAT-401, se reconocen sin importar el año en que fueron aprobadas; el estudiante que migra cursa las asignaturas del Rediseño Curricular que no tienen equivalente aprobado, con sujeción a sus prerrequisitos.</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr"/>
@@ -16380,7 +16368,7 @@
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1.4</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -16390,12 +16378,12 @@
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>Primera promoción del Plan 2027</t>
+          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Plan 2027. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de actualizació</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>Primera promoción del Rediseño Curricular</t>
+          <t>Los docentes titulares conservan su cátedra en la asignatura equivalente del Rediseño Curricular. Cuando la carga horaria de la asignatura disminuye, la diferencia se compensa conforme al punto 16.1.2, y cuando el contenido se actualiza, el docente participa de forma obligatoria en el programa de ac</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr"/>
@@ -16414,20 +16402,24 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Denominación del grado (Reglamento 08, Art. 4)</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Plan 2027, el Honorable </t>
+          <t>Técnico Universitario Superior en Contabilidad General</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Rediseño Curricular, el </t>
-        </is>
-      </c>
-      <c r="E225" s="7" t="inlineStr"/>
+          <t>Técnico Superior en Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Habilitación de la salida intermedia de Técnico Universitario Superior en Contabilidad General; planes de asignatura de </t>
+        </is>
+      </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16438,25 +16430,29 @@
     <row r="226">
       <c r="A226" s="8" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>Término: Rediseño Curricular</t>
+          <t>Referencia cruzada</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
         <is>
-          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Plan 2027 ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
+          <t>12.1.5.</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Rediseño Curricular ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
-        </is>
-      </c>
-      <c r="E226" s="7" t="inlineStr"/>
+          <t>12.1.3.</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>Fuente: elaboración con base en los puntos 11.3.4 y 12.1.5.</t>
+        </is>
+      </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
           <t>En proceso</t>
@@ -16467,7 +16463,7 @@
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -16477,12 +16473,12 @@
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Plan 2027, con reconocimiento en su historial académico.</t>
+          <t>Cuadro 2. Cronograma de implementación del Plan 2027</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Rediseño Curricular, con reconocimiento en su historial académico.</t>
+          <t>Cuadro 2. Cronograma de implementación del Rediseño Curricular</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr"/>
@@ -16496,7 +16492,7 @@
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -16506,12 +16502,12 @@
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Plan 2027 o el PETAENG, conforme al punto 13.1.4.</t>
+          <t>Plan de Estudios 2027</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Rediseño Curricular o el PETAENG, conforme al punto 13.1.4.</t>
+          <t>Rediseño Curricular</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr"/>
@@ -16522,9 +16518,154 @@
       </c>
       <c r="G228" s="10" t="n"/>
     </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
+        <is>
+          <t>Primera promoción del Plan 2027</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>Primera promoción del Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr"/>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G229" s="10" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Plan 2027, el Honorable </t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Dirección de Carrera es responsable de la ejecución del plan de implementación, con el apoyo de la Comisión de Evaluación Curricular, la Comisión de Convalidaciones, la Unidad de Kárdex Académico, el Centro de Cómputo y las jefaturas de área. Antes de iniciar cada año del Rediseño Curricular, el </t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr"/>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G230" s="10" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C231" s="7" t="inlineStr">
+        <is>
+          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Plan 2027 ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>Cada año del Plan 2013 se extingue cuando el año equivalente del Rediseño Curricular ya está en funcionamiento, según el Cuadro 2, de modo que el estudiante siempre dispone de una asignatura equivalente para continuar sus estudios.</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr"/>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G231" s="10" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Plan 2027, con reconocimiento en su historial académico.</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que repruebe o no haya cursado una asignatura del Plan 2013 después de su extinción la cursa en la asignatura equivalente del Rediseño Curricular, con reconocimiento en su historial académico.</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr"/>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>Término: Rediseño Curricular</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Plan 2027 o el PETAENG, conforme al punto 13.1.4.</t>
+        </is>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>El estudiante que concluya el Plan 2013 dispone de un plazo de hasta tres años calendario desde su egreso para graduarse conforme a la reglamentación de ese plan. Vencido el plazo, se gradúa mediante las modalidades del Rediseño Curricular o el PETAENG, conforme al punto 13.1.4.</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr"/>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="G233" s="10" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G228"/>
-  <conditionalFormatting sqref="F4:F228">
+  <autoFilter ref="A3:G233"/>
+  <conditionalFormatting sqref="F4:F233">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F4="Corregido"</formula>
     </cfRule>
@@ -16539,7 +16680,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F4:F228" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F233" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En proceso,Corregido,No aplica"</formula1>
     </dataValidation>
   </dataValidations>
